--- a/research/traditional_assets/database/data/denmark/denmark_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_software_system_application.xlsx
@@ -2023,7 +2023,7 @@
         <v>0.58472304682501</v>
       </c>
       <c r="H2">
-        <v>2.78770896379322</v>
+        <v>2.78770896379321</v>
       </c>
       <c r="I2">
         <v>0.0146825274120641</v>
@@ -2162,7 +2162,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2299,22 +2299,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1011486268241594</v>
+        <v>0.1009611998451463</v>
       </c>
       <c r="C2">
-        <v>492.5140274509283</v>
+        <v>489.2420486160332</v>
       </c>
       <c r="D2">
-        <v>492.2650274509282</v>
+        <v>493.937647829527</v>
       </c>
       <c r="E2">
-        <v>-7.259921349379324</v>
+        <v>-2.31532213588553</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.944599213493793</v>
       </c>
       <c r="G2">
         <v>0.249</v>
@@ -2335,28 +2335,28 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2487133404387378</v>
       </c>
       <c r="N2">
-        <v>9.136000000000001</v>
+        <v>8.887286659561264</v>
       </c>
       <c r="O2">
-        <v>2.00992</v>
+        <v>1.955203065103478</v>
       </c>
       <c r="P2">
-        <v>7.126080000000001</v>
+        <v>6.932083594457786</v>
       </c>
       <c r="Q2">
-        <v>10.40608</v>
+        <v>10.21208359445779</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1011486268241594</v>
+        <v>0.1015847069142892</v>
       </c>
       <c r="T2">
-        <v>1.278259280003682</v>
+        <v>1.288330413724923</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>36.73305172888524</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1009611998451463</v>
+        <v>0.1007737728661331</v>
       </c>
       <c r="C3">
-        <v>489.2420486160332</v>
+        <v>485.9814750083314</v>
       </c>
       <c r="D3">
-        <v>493.937647829527</v>
+        <v>495.6216734353189</v>
       </c>
       <c r="E3">
-        <v>-2.31532213588553</v>
+        <v>2.629277077608263</v>
       </c>
       <c r="F3">
-        <v>4.944599213493793</v>
+        <v>9.889198426987587</v>
       </c>
       <c r="G3">
         <v>0.249</v>
@@ -2417,28 +2417,28 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M3">
-        <v>0.2487133404387378</v>
+        <v>0.4974266808774756</v>
       </c>
       <c r="N3">
-        <v>8.887286659561264</v>
+        <v>8.638573319122525</v>
       </c>
       <c r="O3">
-        <v>1.955203065103478</v>
+        <v>1.900486130206956</v>
       </c>
       <c r="P3">
-        <v>6.932083594457786</v>
+        <v>6.73808718891557</v>
       </c>
       <c r="Q3">
-        <v>10.21208359445779</v>
+        <v>10.01808718891557</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1015847069142892</v>
+        <v>0.102029686598095</v>
       </c>
       <c r="T3">
-        <v>1.288330413724923</v>
+        <v>1.298607080787414</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>36.73305172888524</v>
+        <v>18.36652586444262</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1007737728661331</v>
+        <v>0.10062144588712</v>
       </c>
       <c r="C4">
-        <v>485.9814750083314</v>
+        <v>482.4140111663361</v>
       </c>
       <c r="D4">
-        <v>495.6216734353189</v>
+        <v>496.9988088068175</v>
       </c>
       <c r="E4">
-        <v>2.629277077608263</v>
+        <v>7.573876291102055</v>
       </c>
       <c r="F4">
-        <v>9.889198426987587</v>
+        <v>14.83379764048138</v>
       </c>
       <c r="G4">
         <v>0.249</v>
@@ -2499,45 +2499,45 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M4">
-        <v>0.4974266808774756</v>
+        <v>0.7683907177769354</v>
       </c>
       <c r="N4">
-        <v>8.638573319122525</v>
+        <v>8.367609282223066</v>
       </c>
       <c r="O4">
-        <v>1.900486130206956</v>
+        <v>1.840874042089075</v>
       </c>
       <c r="P4">
-        <v>6.73808718891557</v>
+        <v>6.526735240133991</v>
       </c>
       <c r="Q4">
-        <v>10.01808718891557</v>
+        <v>9.806735240133991</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.102029686598095</v>
+        <v>0.1024838411207422</v>
       </c>
       <c r="T4">
-        <v>1.298607080787414</v>
+        <v>1.309095637892431</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V4">
         <v>0.22</v>
       </c>
       <c r="W4">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y4">
-        <v>18.36652586444262</v>
+        <v>11.88978443991588</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.10062144588712</v>
+        <v>0.1004987589081068</v>
       </c>
       <c r="C5">
-        <v>482.4140111663361</v>
+        <v>478.5841590447843</v>
       </c>
       <c r="D5">
-        <v>496.9988088068175</v>
+        <v>498.1135558987594</v>
       </c>
       <c r="E5">
-        <v>7.573876291102055</v>
+        <v>12.51847550459585</v>
       </c>
       <c r="F5">
-        <v>14.83379764048138</v>
+        <v>19.77839685397517</v>
       </c>
       <c r="G5">
         <v>0.249</v>
@@ -2581,45 +2581,45 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M5">
-        <v>0.7683907177769354</v>
+        <v>1.058144231687672</v>
       </c>
       <c r="N5">
-        <v>8.367609282223066</v>
+        <v>8.077855768312329</v>
       </c>
       <c r="O5">
-        <v>1.840874042089075</v>
+        <v>1.777128269028712</v>
       </c>
       <c r="P5">
-        <v>6.526735240133991</v>
+        <v>6.300727499283616</v>
       </c>
       <c r="Q5">
-        <v>9.806735240133991</v>
+        <v>9.580727499283617</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1024838411207422</v>
+        <v>0.1029474571959446</v>
       </c>
       <c r="T5">
-        <v>1.309095637892431</v>
+        <v>1.319802706603801</v>
       </c>
       <c r="U5">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.22</v>
       </c>
       <c r="W5">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>11.88978443991588</v>
+        <v>8.633983654032372</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1004987589081068</v>
+        <v>0.1003674919290937</v>
       </c>
       <c r="C6">
-        <v>478.5841590447843</v>
+        <v>474.8378165108038</v>
       </c>
       <c r="D6">
-        <v>498.1135558987594</v>
+        <v>499.3118125782727</v>
       </c>
       <c r="E6">
-        <v>12.51847550459585</v>
+        <v>17.46307471808964</v>
       </c>
       <c r="F6">
-        <v>19.77839685397517</v>
+        <v>24.72299606746897</v>
       </c>
       <c r="G6">
         <v>0.249</v>
@@ -2663,45 +2663,45 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M6">
-        <v>1.058144231687672</v>
+        <v>1.342458686463565</v>
       </c>
       <c r="N6">
-        <v>8.077855768312329</v>
+        <v>7.793541313536436</v>
       </c>
       <c r="O6">
-        <v>1.777128269028712</v>
+        <v>1.714579088978016</v>
       </c>
       <c r="P6">
-        <v>6.300727499283616</v>
+        <v>6.078962224558421</v>
       </c>
       <c r="Q6">
-        <v>9.580727499283617</v>
+        <v>9.35896222455842</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1029474571959446</v>
+        <v>0.1034208336095723</v>
       </c>
       <c r="T6">
-        <v>1.319802706603801</v>
+        <v>1.330735187288044</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V6">
         <v>0.22</v>
       </c>
       <c r="W6">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y6">
-        <v>8.633983654032372</v>
+        <v>6.80542357997395</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1003674919290937</v>
+        <v>0.1002580649500805</v>
       </c>
       <c r="C7">
-        <v>474.8378165108038</v>
+        <v>470.8965247649203</v>
       </c>
       <c r="D7">
-        <v>499.3118125782727</v>
+        <v>500.315120045883</v>
       </c>
       <c r="E7">
-        <v>17.46307471808964</v>
+        <v>22.40767393158344</v>
       </c>
       <c r="F7">
-        <v>24.72299606746897</v>
+        <v>29.66759528096276</v>
       </c>
       <c r="G7">
         <v>0.249</v>
@@ -2745,45 +2745,45 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M7">
-        <v>1.342458686463565</v>
+        <v>1.640618019037241</v>
       </c>
       <c r="N7">
-        <v>7.793541313536436</v>
+        <v>7.49538198096276</v>
       </c>
       <c r="O7">
-        <v>1.714579088978016</v>
+        <v>1.648984035811807</v>
       </c>
       <c r="P7">
-        <v>6.078962224558421</v>
+        <v>5.846397945150953</v>
       </c>
       <c r="Q7">
-        <v>9.35896222455842</v>
+        <v>9.126397945150952</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1034208336095723</v>
+        <v>0.1039042818617878</v>
       </c>
       <c r="T7">
-        <v>1.330735187288044</v>
+        <v>1.341900273944291</v>
       </c>
       <c r="U7">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y7">
-        <v>6.80542357997395</v>
+        <v>5.568633218694778</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1002580649500805</v>
+        <v>0.1001096379710674</v>
       </c>
       <c r="C8">
-        <v>470.8965247649203</v>
+        <v>467.3192751526624</v>
       </c>
       <c r="D8">
-        <v>500.315120045883</v>
+        <v>501.6824696471189</v>
       </c>
       <c r="E8">
-        <v>22.40767393158343</v>
+        <v>27.35227314507723</v>
       </c>
       <c r="F8">
-        <v>29.66759528096276</v>
+        <v>34.61219449445655</v>
       </c>
       <c r="G8">
         <v>0.249</v>
@@ -2827,28 +2827,28 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M8">
-        <v>1.640618019037241</v>
+        <v>1.914054355543447</v>
       </c>
       <c r="N8">
-        <v>7.49538198096276</v>
+        <v>7.221945644456554</v>
       </c>
       <c r="O8">
-        <v>1.648984035811807</v>
+        <v>1.588828041780442</v>
       </c>
       <c r="P8">
-        <v>5.846397945150953</v>
+        <v>5.633117602676112</v>
       </c>
       <c r="Q8">
-        <v>9.126397945150952</v>
+        <v>8.913117602676111</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1039042818617878</v>
+        <v>0.1043981268506101</v>
       </c>
       <c r="T8">
-        <v>1.341900273944291</v>
+        <v>1.353305469990995</v>
       </c>
       <c r="U8">
         <v>0.0553</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>5.568633218694779</v>
+        <v>4.773114187452667</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1001096379710674</v>
+        <v>0.1003356109920542</v>
       </c>
       <c r="C9">
-        <v>467.3192751526623</v>
+        <v>460.2959112351512</v>
       </c>
       <c r="D9">
-        <v>501.6824696471189</v>
+        <v>499.6037049431015</v>
       </c>
       <c r="E9">
-        <v>27.35227314507723</v>
+        <v>32.29687235857102</v>
       </c>
       <c r="F9">
-        <v>34.61219449445656</v>
+        <v>39.55679370795035</v>
       </c>
       <c r="G9">
         <v>0.249</v>
@@ -2909,45 +2909,45 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M9">
-        <v>1.914054355543448</v>
+        <v>2.424831454297356</v>
       </c>
       <c r="N9">
-        <v>7.221945644456554</v>
+        <v>6.711168545702645</v>
       </c>
       <c r="O9">
-        <v>1.588828041780442</v>
+        <v>1.476457080054582</v>
       </c>
       <c r="P9">
-        <v>5.633117602676112</v>
+        <v>5.234711465648063</v>
       </c>
       <c r="Q9">
-        <v>8.913117602676111</v>
+        <v>8.514711465648062</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1043981268506101</v>
+        <v>0.1049027076000589</v>
       </c>
       <c r="T9">
-        <v>1.353305469990995</v>
+        <v>1.364958605082192</v>
       </c>
       <c r="U9">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.04313400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>4.773114187452666</v>
+        <v>3.767684547232723</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1003356109920542</v>
+        <v>0.1004305440130411</v>
       </c>
       <c r="C10">
-        <v>460.2959112351512</v>
+        <v>454.4831367203983</v>
       </c>
       <c r="D10">
-        <v>499.6037049431015</v>
+        <v>498.7355296418424</v>
       </c>
       <c r="E10">
-        <v>32.29687235857102</v>
+        <v>37.24147157206481</v>
       </c>
       <c r="F10">
-        <v>39.55679370795035</v>
+        <v>44.50139292144414</v>
       </c>
       <c r="G10">
         <v>0.249</v>
@@ -2991,45 +2991,45 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M10">
-        <v>2.424831454297356</v>
+        <v>2.852539286264569</v>
       </c>
       <c r="N10">
-        <v>6.711168545702645</v>
+        <v>6.283460713735431</v>
       </c>
       <c r="O10">
-        <v>1.476457080054582</v>
+        <v>1.382361357021795</v>
       </c>
       <c r="P10">
-        <v>5.234711465648063</v>
+        <v>4.901099356713637</v>
       </c>
       <c r="Q10">
-        <v>8.514711465648062</v>
+        <v>8.181099356713636</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1049027076000589</v>
+        <v>0.1054183780363089</v>
       </c>
       <c r="T10">
-        <v>1.364958605082192</v>
+        <v>1.376867853032537</v>
       </c>
       <c r="U10">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V10">
         <v>0.22</v>
       </c>
       <c r="W10">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y10">
-        <v>3.767684547232723</v>
+        <v>3.202760447153628</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1004305440130411</v>
+        <v>0.1009591570340279</v>
       </c>
       <c r="C11">
-        <v>454.4831367203983</v>
+        <v>444.7589486013889</v>
       </c>
       <c r="D11">
-        <v>498.7355296418424</v>
+        <v>493.9559407363267</v>
       </c>
       <c r="E11">
-        <v>37.24147157206481</v>
+        <v>42.18607078555861</v>
       </c>
       <c r="F11">
-        <v>44.50139292144414</v>
+        <v>49.44599213493793</v>
       </c>
       <c r="G11">
         <v>0.249</v>
@@ -3073,45 +3073,45 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M11">
-        <v>2.852539286264569</v>
+        <v>3.555166834502038</v>
       </c>
       <c r="N11">
-        <v>6.283460713735431</v>
+        <v>5.580833165497964</v>
       </c>
       <c r="O11">
-        <v>1.382361357021795</v>
+        <v>1.227783296409552</v>
       </c>
       <c r="P11">
-        <v>4.901099356713637</v>
+        <v>4.353049869088412</v>
       </c>
       <c r="Q11">
-        <v>8.181099356713636</v>
+        <v>7.633049869088412</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1054183780363089</v>
+        <v>0.1059455078155866</v>
       </c>
       <c r="T11">
-        <v>1.376867853032537</v>
+        <v>1.389041750937334</v>
       </c>
       <c r="U11">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V11">
         <v>0.22</v>
       </c>
       <c r="W11">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>3.202760447153628</v>
+        <v>2.569780948488077</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1009591570340279</v>
+        <v>0.1012748300550148</v>
       </c>
       <c r="C12">
-        <v>444.7589486013887</v>
+        <v>437.003550979103</v>
       </c>
       <c r="D12">
-        <v>493.9559407363266</v>
+        <v>491.1451423275346</v>
       </c>
       <c r="E12">
-        <v>42.18607078555861</v>
+        <v>47.1306699990524</v>
       </c>
       <c r="F12">
-        <v>49.44599213493794</v>
+        <v>54.39059134843173</v>
       </c>
       <c r="G12">
         <v>0.249</v>
@@ -3155,45 +3155,45 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M12">
-        <v>3.555166834502038</v>
+        <v>4.122806824211125</v>
       </c>
       <c r="N12">
-        <v>5.580833165497963</v>
+        <v>5.013193175788876</v>
       </c>
       <c r="O12">
-        <v>1.227783296409552</v>
+        <v>1.102902498673553</v>
       </c>
       <c r="P12">
-        <v>4.353049869088411</v>
+        <v>3.910290677115324</v>
       </c>
       <c r="Q12">
-        <v>7.633049869088412</v>
+        <v>7.190290677115323</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1059455078155866</v>
+        <v>0.1064844832078818</v>
       </c>
       <c r="T12">
-        <v>1.389041750937334</v>
+        <v>1.401489219581565</v>
       </c>
       <c r="U12">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y12">
-        <v>2.569780948488077</v>
+        <v>2.215966061361151</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1012748300550148</v>
+        <v>0.1012863030760016</v>
       </c>
       <c r="C13">
-        <v>437.003550979103</v>
+        <v>431.9573966391523</v>
       </c>
       <c r="D13">
-        <v>491.1451423275346</v>
+        <v>491.0435872010778</v>
       </c>
       <c r="E13">
-        <v>47.1306699990524</v>
+        <v>52.07526921254619</v>
       </c>
       <c r="F13">
-        <v>54.39059134843173</v>
+        <v>59.33519056192551</v>
       </c>
       <c r="G13">
         <v>0.249</v>
@@ -3237,28 +3237,28 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M13">
-        <v>4.122806824211125</v>
+        <v>4.497607444593954</v>
       </c>
       <c r="N13">
-        <v>5.013193175788876</v>
+        <v>4.638392555406047</v>
       </c>
       <c r="O13">
-        <v>1.102902498673553</v>
+        <v>1.02044636218933</v>
       </c>
       <c r="P13">
-        <v>3.910290677115324</v>
+        <v>3.617946193216717</v>
       </c>
       <c r="Q13">
-        <v>7.190290677115323</v>
+        <v>6.897946193216717</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1064844832078818</v>
+        <v>0.1070357080409109</v>
       </c>
       <c r="T13">
-        <v>1.401489219581565</v>
+        <v>1.414219585240437</v>
       </c>
       <c r="U13">
         <v>0.07580000000000001</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>2.215966061361151</v>
+        <v>2.031302222914388</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1012863030760016</v>
+        <v>0.1027376560969885</v>
       </c>
       <c r="C14">
-        <v>431.9573966391523</v>
+        <v>414.495991456222</v>
       </c>
       <c r="D14">
-        <v>491.0435872010778</v>
+        <v>478.5267812316413</v>
       </c>
       <c r="E14">
-        <v>52.07526921254619</v>
+        <v>57.01986842603999</v>
       </c>
       <c r="F14">
-        <v>59.33519056192551</v>
+        <v>64.27978977541932</v>
       </c>
       <c r="G14">
         <v>0.249</v>
@@ -3319,45 +3319,45 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M14">
-        <v>4.497607444593954</v>
+        <v>5.785181079787739</v>
       </c>
       <c r="N14">
-        <v>4.638392555406047</v>
+        <v>3.350818920212262</v>
       </c>
       <c r="O14">
-        <v>1.02044636218933</v>
+        <v>0.7371801624466977</v>
       </c>
       <c r="P14">
-        <v>3.617946193216717</v>
+        <v>2.613638757765564</v>
       </c>
       <c r="Q14">
-        <v>6.897946193216717</v>
+        <v>5.893638757765564</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1070357080409109</v>
+        <v>0.1075996047091821</v>
       </c>
       <c r="T14">
-        <v>1.414219585240437</v>
+        <v>1.427242602983421</v>
       </c>
       <c r="U14">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V14">
         <v>0.22</v>
       </c>
       <c r="W14">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>2.031302222914388</v>
+        <v>1.579207266634981</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1027376560969885</v>
+        <v>0.1096911485543798</v>
       </c>
       <c r="C15">
-        <v>414.495991456222</v>
+        <v>357.4716841886165</v>
       </c>
       <c r="D15">
-        <v>478.5267812316413</v>
+        <v>426.4470731775295</v>
       </c>
       <c r="E15">
-        <v>57.01986842603999</v>
+        <v>61.96446763953379</v>
       </c>
       <c r="F15">
-        <v>64.27978977541932</v>
+        <v>69.22438898891312</v>
       </c>
       <c r="G15">
         <v>0.249</v>
@@ -3401,45 +3401,45 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M15">
-        <v>5.785181079787739</v>
+        <v>10.16214030357245</v>
       </c>
       <c r="N15">
-        <v>3.350818920212262</v>
+        <v>-1.026140303572445</v>
       </c>
       <c r="O15">
-        <v>0.7371801624466977</v>
+        <v>-0.2257508667859379</v>
       </c>
       <c r="P15">
-        <v>2.613638757765564</v>
+        <v>-0.8003894367865073</v>
       </c>
       <c r="Q15">
-        <v>5.893638757765564</v>
+        <v>2.479610563213492</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1075996047091821</v>
+        <v>0.1083767768124398</v>
       </c>
       <c r="T15">
-        <v>1.427242602983421</v>
+        <v>1.445191150402768</v>
       </c>
       <c r="U15">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V15">
-        <v>0.22</v>
+        <v>0.1977851062825243</v>
       </c>
       <c r="W15">
-        <v>0.0702</v>
+        <v>0.1177651463977254</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y15">
-        <v>1.579207266634981</v>
+        <v>0.8990232103751106</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1096911485543798</v>
+        <v>0.1107011485543798</v>
       </c>
       <c r="C16">
-        <v>357.4716841886165</v>
+        <v>345.8906609132524</v>
       </c>
       <c r="D16">
-        <v>426.4470731775295</v>
+        <v>419.8106491156593</v>
       </c>
       <c r="E16">
-        <v>61.96446763953379</v>
+        <v>66.90906685302758</v>
       </c>
       <c r="F16">
-        <v>69.22438898891312</v>
+        <v>74.16898820240691</v>
       </c>
       <c r="G16">
         <v>0.249</v>
@@ -3483,37 +3483,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M16">
-        <v>10.16214030357245</v>
+        <v>10.88800746811333</v>
       </c>
       <c r="N16">
-        <v>-1.026140303572445</v>
+        <v>-1.752007468113334</v>
       </c>
       <c r="O16">
-        <v>-0.2257508667859379</v>
+        <v>-0.3854416429849334</v>
       </c>
       <c r="P16">
-        <v>-0.8003894367865073</v>
+        <v>-1.3665658251284</v>
       </c>
       <c r="Q16">
-        <v>2.479610563213492</v>
+        <v>1.9134341748716</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1083767768124398</v>
+        <v>0.1091129741867038</v>
       </c>
       <c r="T16">
-        <v>1.445191150402768</v>
+        <v>1.462193399231036</v>
       </c>
       <c r="U16">
         <v>0.1468</v>
       </c>
       <c r="V16">
-        <v>0.1977851062825243</v>
+        <v>0.184599432530356</v>
       </c>
       <c r="W16">
-        <v>0.1177651463977254</v>
+        <v>0.1197008033045437</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.8990232103751106</v>
+        <v>0.8390883296834366</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1107011485543798</v>
+        <v>0.1207633016088365</v>
       </c>
       <c r="C17">
-        <v>345.8906609132524</v>
+        <v>284.5958354605951</v>
       </c>
       <c r="D17">
-        <v>419.8106491156593</v>
+        <v>363.4604228764958</v>
       </c>
       <c r="E17">
-        <v>66.90906685302757</v>
+        <v>71.85366606652137</v>
       </c>
       <c r="F17">
-        <v>74.16898820240689</v>
+        <v>79.1135874159007</v>
       </c>
       <c r="G17">
         <v>0.249</v>
@@ -3565,45 +3565,45 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M17">
-        <v>10.88800746811333</v>
+        <v>15.88600835311286</v>
       </c>
       <c r="N17">
-        <v>-1.752007468113332</v>
+        <v>-6.750008353112859</v>
       </c>
       <c r="O17">
-        <v>-0.3854416429849331</v>
+        <v>-1.485001837684829</v>
       </c>
       <c r="P17">
-        <v>-1.366565825128399</v>
+        <v>-5.265006515428031</v>
       </c>
       <c r="Q17">
-        <v>1.913434174871601</v>
+        <v>-1.985006515428031</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1091129741867038</v>
+        <v>0.1103573584680416</v>
       </c>
       <c r="T17">
-        <v>1.462193399231036</v>
+        <v>1.490932066236527</v>
       </c>
       <c r="U17">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V17">
-        <v>0.1845994325303561</v>
+        <v>0.1265213989142941</v>
       </c>
       <c r="W17">
-        <v>0.1197008033045437</v>
+        <v>0.1753945030980097</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y17">
-        <v>0.8390883296834367</v>
+        <v>0.5750972677922459</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1207633016088365</v>
+        <v>0.1223133016088365</v>
       </c>
       <c r="C18">
-        <v>284.5958354605951</v>
+        <v>272.2882857063094</v>
       </c>
       <c r="D18">
-        <v>363.4604228764958</v>
+        <v>356.0974723357038</v>
       </c>
       <c r="E18">
-        <v>71.85366606652137</v>
+        <v>76.79826528001517</v>
       </c>
       <c r="F18">
-        <v>79.1135874159007</v>
+        <v>84.0581866293945</v>
       </c>
       <c r="G18">
         <v>0.249</v>
@@ -3647,37 +3647,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M18">
-        <v>15.88600835311286</v>
+        <v>16.87888387518242</v>
       </c>
       <c r="N18">
-        <v>-6.750008353112859</v>
+        <v>-7.742883875182416</v>
       </c>
       <c r="O18">
-        <v>-1.485001837684829</v>
+        <v>-1.703434452540131</v>
       </c>
       <c r="P18">
-        <v>-5.265006515428031</v>
+        <v>-6.039449422642285</v>
       </c>
       <c r="Q18">
-        <v>-1.985006515428031</v>
+        <v>-2.759449422642285</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1103573584680416</v>
+        <v>0.1111351579676566</v>
       </c>
       <c r="T18">
-        <v>1.490932066236527</v>
+        <v>1.508895103179136</v>
       </c>
       <c r="U18">
         <v>0.2008</v>
       </c>
       <c r="V18">
-        <v>0.1265213989142941</v>
+        <v>0.1190789636840415</v>
       </c>
       <c r="W18">
-        <v>0.1753945030980097</v>
+        <v>0.1768889440922445</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.5750972677922459</v>
+        <v>0.5412680167456431</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1223133016088365</v>
+        <v>0.1238633016088365</v>
       </c>
       <c r="C19">
-        <v>272.2882857063094</v>
+        <v>260.2731287435919</v>
       </c>
       <c r="D19">
-        <v>356.0974723357038</v>
+        <v>349.0269145864801</v>
       </c>
       <c r="E19">
-        <v>76.79826528001517</v>
+        <v>81.74286449350896</v>
       </c>
       <c r="F19">
-        <v>84.0581866293945</v>
+        <v>89.00278584288829</v>
       </c>
       <c r="G19">
         <v>0.249</v>
@@ -3729,37 +3729,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M19">
-        <v>16.87888387518242</v>
+        <v>17.87175939725197</v>
       </c>
       <c r="N19">
-        <v>-7.742883875182416</v>
+        <v>-8.735759397251966</v>
       </c>
       <c r="O19">
-        <v>-1.703434452540131</v>
+        <v>-1.921867067395433</v>
       </c>
       <c r="P19">
-        <v>-6.039449422642285</v>
+        <v>-6.813892329856534</v>
       </c>
       <c r="Q19">
-        <v>-2.759449422642285</v>
+        <v>-3.533892329856534</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1111351579676566</v>
+        <v>0.1119319281867744</v>
       </c>
       <c r="T19">
-        <v>1.508895103179136</v>
+        <v>1.527296262974003</v>
       </c>
       <c r="U19">
         <v>0.2008</v>
       </c>
       <c r="V19">
-        <v>0.1190789636840415</v>
+        <v>0.1124634657015947</v>
       </c>
       <c r="W19">
-        <v>0.1768889440922445</v>
+        <v>0.1782173360871198</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.5412680167456431</v>
+        <v>0.5111975713708852</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1238633016088365</v>
+        <v>0.1322296103445666</v>
       </c>
       <c r="C20">
-        <v>260.2731287435918</v>
+        <v>221.5430373490222</v>
       </c>
       <c r="D20">
-        <v>349.0269145864801</v>
+        <v>315.2414224054043</v>
       </c>
       <c r="E20">
-        <v>81.74286449350895</v>
+        <v>86.68746370700275</v>
       </c>
       <c r="F20">
-        <v>89.00278584288827</v>
+        <v>93.94738505638207</v>
       </c>
       <c r="G20">
         <v>0.249</v>
@@ -3811,45 +3811,45 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M20">
-        <v>17.87175939725197</v>
+        <v>22.15279339629489</v>
       </c>
       <c r="N20">
-        <v>-8.735759397251966</v>
+        <v>-13.01679339629489</v>
       </c>
       <c r="O20">
-        <v>-1.921867067395433</v>
+        <v>-2.863694547184876</v>
       </c>
       <c r="P20">
-        <v>-6.813892329856534</v>
+        <v>-10.15309884911002</v>
       </c>
       <c r="Q20">
-        <v>-3.533892329856534</v>
+        <v>-6.873098849110017</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1119319281867744</v>
+        <v>0.112953691171463</v>
       </c>
       <c r="T20">
-        <v>1.527296262974003</v>
+        <v>1.550893560541871</v>
       </c>
       <c r="U20">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.1124634657015947</v>
+        <v>0.09072986706661401</v>
       </c>
       <c r="W20">
-        <v>0.1782173360871198</v>
+        <v>0.2144058973456924</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y20">
-        <v>0.5111975713708852</v>
+        <v>0.4124084866664273</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1322296103445666</v>
+        <v>0.1341296103445666</v>
       </c>
       <c r="C21">
-        <v>221.5430373490222</v>
+        <v>209.8174877811254</v>
       </c>
       <c r="D21">
-        <v>315.2414224054043</v>
+        <v>308.4604720510013</v>
       </c>
       <c r="E21">
-        <v>86.68746370700275</v>
+        <v>91.63206292049655</v>
       </c>
       <c r="F21">
-        <v>93.94738505638207</v>
+        <v>98.89198426987588</v>
       </c>
       <c r="G21">
         <v>0.249</v>
@@ -3893,37 +3893,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M21">
-        <v>22.15279339629489</v>
+        <v>23.31872989083673</v>
       </c>
       <c r="N21">
-        <v>-13.01679339629489</v>
+        <v>-14.18272989083673</v>
       </c>
       <c r="O21">
-        <v>-2.863694547184876</v>
+        <v>-3.120200575984081</v>
       </c>
       <c r="P21">
-        <v>-10.15309884911002</v>
+        <v>-11.06252931485265</v>
       </c>
       <c r="Q21">
-        <v>-6.873098849110017</v>
+        <v>-7.782529314852651</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.112953691171463</v>
+        <v>0.1137931123111063</v>
       </c>
       <c r="T21">
-        <v>1.550893560541871</v>
+        <v>1.570279730048645</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.09072986706661401</v>
+        <v>0.0861933737132833</v>
       </c>
       <c r="W21">
-        <v>0.2144058973456924</v>
+        <v>0.2154756024784078</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.4124084866664273</v>
+        <v>0.3917880623331059</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1341296103445666</v>
+        <v>0.1360296103445666</v>
       </c>
       <c r="C22">
-        <v>209.8174877811254</v>
+        <v>198.3775164313803</v>
       </c>
       <c r="D22">
-        <v>308.4604720510013</v>
+        <v>301.9650999147499</v>
       </c>
       <c r="E22">
-        <v>91.63206292049655</v>
+        <v>96.57666213399034</v>
       </c>
       <c r="F22">
-        <v>98.89198426987588</v>
+        <v>103.8365834833697</v>
       </c>
       <c r="G22">
         <v>0.249</v>
@@ -3975,37 +3975,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M22">
-        <v>23.31872989083673</v>
+        <v>24.48466638537857</v>
       </c>
       <c r="N22">
-        <v>-14.18272989083673</v>
+        <v>-15.34866638537857</v>
       </c>
       <c r="O22">
-        <v>-3.120200575984081</v>
+        <v>-3.376706604783285</v>
       </c>
       <c r="P22">
-        <v>-11.06252931485265</v>
+        <v>-11.97195978059528</v>
       </c>
       <c r="Q22">
-        <v>-7.782529314852651</v>
+        <v>-8.691959780595282</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1137931123111063</v>
+        <v>0.1146537846188418</v>
       </c>
       <c r="T22">
-        <v>1.570279730048645</v>
+        <v>1.590156688656856</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.0861933737132833</v>
+        <v>0.08208892734598409</v>
       </c>
       <c r="W22">
-        <v>0.2154756024784078</v>
+        <v>0.216443430931817</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3917880623331059</v>
+        <v>0.3731314879362914</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1360296103445666</v>
+        <v>0.1379296103445666</v>
       </c>
       <c r="C23">
-        <v>198.3775164313804</v>
+        <v>187.2054547582902</v>
       </c>
       <c r="D23">
-        <v>301.9650999147501</v>
+        <v>295.7376374551537</v>
       </c>
       <c r="E23">
-        <v>96.57666213399033</v>
+        <v>101.5212613474841</v>
       </c>
       <c r="F23">
-        <v>103.8365834833697</v>
+        <v>108.7811826968635</v>
       </c>
       <c r="G23">
         <v>0.249</v>
@@ -4057,37 +4057,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M23">
-        <v>24.48466638537856</v>
+        <v>25.6506028799204</v>
       </c>
       <c r="N23">
-        <v>-15.34866638537856</v>
+        <v>-16.5146028799204</v>
       </c>
       <c r="O23">
-        <v>-3.376706604783284</v>
+        <v>-3.633212633582489</v>
       </c>
       <c r="P23">
-        <v>-11.97195978059528</v>
+        <v>-12.88139024633792</v>
       </c>
       <c r="Q23">
-        <v>-8.69195978059528</v>
+        <v>-9.601390246337916</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1146537846188418</v>
+        <v>0.1155365254472885</v>
       </c>
       <c r="T23">
-        <v>1.590156688656855</v>
+        <v>1.610543312870405</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.08208892734598411</v>
+        <v>0.07835761246662118</v>
       </c>
       <c r="W23">
-        <v>0.2164434309318169</v>
+        <v>0.2173232749803707</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.3731314879362914</v>
+        <v>0.356170965757369</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1379296103445666</v>
+        <v>0.1398296103445666</v>
       </c>
       <c r="C24">
-        <v>187.2054547582902</v>
+        <v>176.2850622908871</v>
       </c>
       <c r="D24">
-        <v>295.7376374551537</v>
+        <v>289.7618442012443</v>
       </c>
       <c r="E24">
-        <v>101.5212613474841</v>
+        <v>106.4658605609779</v>
       </c>
       <c r="F24">
-        <v>108.7811826968635</v>
+        <v>113.7257819103573</v>
       </c>
       <c r="G24">
         <v>0.249</v>
@@ -4139,37 +4139,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M24">
-        <v>25.6506028799204</v>
+        <v>26.81653937446224</v>
       </c>
       <c r="N24">
-        <v>-16.5146028799204</v>
+        <v>-17.68053937446224</v>
       </c>
       <c r="O24">
-        <v>-3.633212633582489</v>
+        <v>-3.889718662381693</v>
       </c>
       <c r="P24">
-        <v>-12.88139024633792</v>
+        <v>-13.79082071208055</v>
       </c>
       <c r="Q24">
-        <v>-9.601390246337916</v>
+        <v>-10.51082071208055</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1155365254472885</v>
+        <v>0.1164421946089416</v>
       </c>
       <c r="T24">
-        <v>1.610543312870405</v>
+        <v>1.6314594597908</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.07835761246662118</v>
+        <v>0.07495075975068113</v>
       </c>
       <c r="W24">
-        <v>0.2173232749803707</v>
+        <v>0.2181266108507894</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.356170965757369</v>
+        <v>0.3406852715940051</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1398296103445666</v>
+        <v>0.1417296103445666</v>
       </c>
       <c r="C25">
-        <v>176.2850622908871</v>
+        <v>165.6013852055571</v>
       </c>
       <c r="D25">
-        <v>289.7618442012443</v>
+        <v>284.0227663294081</v>
       </c>
       <c r="E25">
-        <v>106.4658605609779</v>
+        <v>111.4104597744717</v>
       </c>
       <c r="F25">
-        <v>113.7257819103573</v>
+        <v>118.670381123851</v>
       </c>
       <c r="G25">
         <v>0.249</v>
@@ -4221,37 +4221,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M25">
-        <v>26.81653937446224</v>
+        <v>27.98247586900408</v>
       </c>
       <c r="N25">
-        <v>-17.68053937446224</v>
+        <v>-18.84647586900407</v>
       </c>
       <c r="O25">
-        <v>-3.889718662381693</v>
+        <v>-4.146224691180897</v>
       </c>
       <c r="P25">
-        <v>-13.79082071208055</v>
+        <v>-14.70025117782318</v>
       </c>
       <c r="Q25">
-        <v>-10.51082071208055</v>
+        <v>-11.42025117782318</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1164421946089416</v>
+        <v>0.1173716971695856</v>
       </c>
       <c r="T25">
-        <v>1.6314594597908</v>
+        <v>1.652926031630152</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.07495075975068113</v>
+        <v>0.07182781142773607</v>
       </c>
       <c r="W25">
-        <v>0.2181266108507894</v>
+        <v>0.2188630020653398</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3406852715940051</v>
+        <v>0.326490051944255</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1417296103445666</v>
+        <v>0.1436296103445666</v>
       </c>
       <c r="C26">
-        <v>165.6013852055572</v>
+        <v>155.1406313827872</v>
       </c>
       <c r="D26">
-        <v>284.0227663294082</v>
+        <v>278.506611720132</v>
       </c>
       <c r="E26">
-        <v>111.4104597744717</v>
+        <v>116.3550589879655</v>
       </c>
       <c r="F26">
-        <v>118.670381123851</v>
+        <v>123.6149803373448</v>
       </c>
       <c r="G26">
         <v>0.249</v>
@@ -4303,37 +4303,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M26">
-        <v>27.98247586900407</v>
+        <v>29.14841236354591</v>
       </c>
       <c r="N26">
-        <v>-18.84647586900407</v>
+        <v>-20.01241236354591</v>
       </c>
       <c r="O26">
-        <v>-4.146224691180897</v>
+        <v>-4.4027307199801</v>
       </c>
       <c r="P26">
-        <v>-14.70025117782318</v>
+        <v>-15.60968164356581</v>
       </c>
       <c r="Q26">
-        <v>-11.42025117782318</v>
+        <v>-12.32968164356581</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1173716971695856</v>
+        <v>0.1183259864651801</v>
       </c>
       <c r="T26">
-        <v>1.652926031630152</v>
+        <v>1.674965045385221</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.07182781142773609</v>
+        <v>0.06895469897062664</v>
       </c>
       <c r="W26">
-        <v>0.2188630020653398</v>
+        <v>0.2195404819827262</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.326490051944255</v>
+        <v>0.3134304498664847</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1436296103445666</v>
+        <v>0.1455296103445666</v>
       </c>
       <c r="C27">
-        <v>155.1406313827872</v>
+        <v>144.8900597460583</v>
       </c>
       <c r="D27">
-        <v>278.506611720132</v>
+        <v>273.2006392968969</v>
       </c>
       <c r="E27">
-        <v>116.3550589879655</v>
+        <v>121.2996582014593</v>
       </c>
       <c r="F27">
-        <v>123.6149803373448</v>
+        <v>128.5595795508386</v>
       </c>
       <c r="G27">
         <v>0.249</v>
@@ -4385,37 +4385,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M27">
-        <v>29.14841236354591</v>
+        <v>30.31434885808775</v>
       </c>
       <c r="N27">
-        <v>-20.01241236354591</v>
+        <v>-21.17834885808775</v>
       </c>
       <c r="O27">
-        <v>-4.4027307199801</v>
+        <v>-4.659236748779305</v>
       </c>
       <c r="P27">
-        <v>-15.60968164356581</v>
+        <v>-16.51911210930844</v>
       </c>
       <c r="Q27">
-        <v>-12.32968164356581</v>
+        <v>-13.23911210930845</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1183259864651801</v>
+        <v>0.1193060673633582</v>
       </c>
       <c r="T27">
-        <v>1.674965045385221</v>
+        <v>1.697599708160697</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.06895469897062664</v>
+        <v>0.06630259516406407</v>
       </c>
       <c r="W27">
-        <v>0.2195404819827262</v>
+        <v>0.2201658480603137</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.3134304498664847</v>
+        <v>0.3013754325639275</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1455296103445666</v>
+        <v>0.1474296103445666</v>
       </c>
       <c r="C28">
-        <v>144.8900597460583</v>
+        <v>134.8378820138217</v>
       </c>
       <c r="D28">
-        <v>273.2006392968969</v>
+        <v>268.0930607781541</v>
       </c>
       <c r="E28">
-        <v>121.2996582014593</v>
+        <v>126.2442574149531</v>
       </c>
       <c r="F28">
-        <v>128.5595795508386</v>
+        <v>133.5041787643324</v>
       </c>
       <c r="G28">
         <v>0.249</v>
@@ -4467,37 +4467,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M28">
-        <v>30.31434885808775</v>
+        <v>31.48028535262959</v>
       </c>
       <c r="N28">
-        <v>-21.17834885808775</v>
+        <v>-22.34428535262959</v>
       </c>
       <c r="O28">
-        <v>-4.659236748779305</v>
+        <v>-4.91574277757851</v>
       </c>
       <c r="P28">
-        <v>-16.51911210930844</v>
+        <v>-17.42854257505108</v>
       </c>
       <c r="Q28">
-        <v>-13.23911210930845</v>
+        <v>-14.14854257505108</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1193060673633582</v>
+        <v>0.1203129997929932</v>
       </c>
       <c r="T28">
-        <v>1.697599708160697</v>
+        <v>1.720854498683446</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.06630259516406407</v>
+        <v>0.06384694349132096</v>
       </c>
       <c r="W28">
-        <v>0.2201658480603137</v>
+        <v>0.2207448907247465</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.3013754325639275</v>
+        <v>0.2902133795060043</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1474296103445666</v>
+        <v>0.1493296103445666</v>
       </c>
       <c r="C29">
-        <v>134.8378820138217</v>
+        <v>124.9731752699009</v>
       </c>
       <c r="D29">
-        <v>268.0930607781541</v>
+        <v>263.1729532477271</v>
       </c>
       <c r="E29">
-        <v>126.2442574149531</v>
+        <v>131.1888566284469</v>
       </c>
       <c r="F29">
-        <v>133.5041787643324</v>
+        <v>138.4487779778262</v>
       </c>
       <c r="G29">
         <v>0.249</v>
@@ -4549,37 +4549,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M29">
-        <v>31.48028535262959</v>
+        <v>32.64622184717143</v>
       </c>
       <c r="N29">
-        <v>-22.34428535262959</v>
+        <v>-23.51022184717142</v>
       </c>
       <c r="O29">
-        <v>-4.91574277757851</v>
+        <v>-5.172248806377713</v>
       </c>
       <c r="P29">
-        <v>-17.42854257505108</v>
+        <v>-18.33797304079371</v>
       </c>
       <c r="Q29">
-        <v>-14.14854257505108</v>
+        <v>-15.05797304079371</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1203129997929932</v>
+        <v>0.1213479025678959</v>
       </c>
       <c r="T29">
-        <v>1.720854498683446</v>
+        <v>1.744755255609606</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.06384694349132096</v>
+        <v>0.06156669550948807</v>
       </c>
       <c r="W29">
-        <v>0.2207448907247465</v>
+        <v>0.2212825731988627</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2902133795060043</v>
+        <v>0.2798486159522185</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1493296103445666</v>
+        <v>0.1512296103445666</v>
       </c>
       <c r="C30">
-        <v>124.9731752699009</v>
+        <v>115.2858039875691</v>
       </c>
       <c r="D30">
-        <v>263.1729532477271</v>
+        <v>258.4301811788891</v>
       </c>
       <c r="E30">
-        <v>131.1888566284469</v>
+        <v>136.1334558419407</v>
       </c>
       <c r="F30">
-        <v>138.4487779778262</v>
+        <v>143.39337719132</v>
       </c>
       <c r="G30">
         <v>0.249</v>
@@ -4631,37 +4631,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M30">
-        <v>32.64622184717143</v>
+        <v>33.81215834171326</v>
       </c>
       <c r="N30">
-        <v>-23.51022184717142</v>
+        <v>-24.67615834171325</v>
       </c>
       <c r="O30">
-        <v>-5.172248806377713</v>
+        <v>-5.428754835176916</v>
       </c>
       <c r="P30">
-        <v>-18.33797304079371</v>
+        <v>-19.24740350653634</v>
       </c>
       <c r="Q30">
-        <v>-15.05797304079371</v>
+        <v>-15.96740350653634</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1213479025678959</v>
+        <v>0.1224119575336409</v>
       </c>
       <c r="T30">
-        <v>1.744755255609606</v>
+        <v>1.769329273294248</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.06156669550948807</v>
+        <v>0.0594437060091609</v>
       </c>
       <c r="W30">
-        <v>0.2212825731988627</v>
+        <v>0.2217831741230399</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2798486159522185</v>
+        <v>0.2701986636780042</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1512296103445666</v>
+        <v>0.1531296103445666</v>
       </c>
       <c r="C31">
-        <v>115.2858039875691</v>
+        <v>105.7663503358308</v>
       </c>
       <c r="D31">
-        <v>258.4301811788891</v>
+        <v>253.8553267406446</v>
       </c>
       <c r="E31">
-        <v>136.1334558419407</v>
+        <v>141.0780550554345</v>
       </c>
       <c r="F31">
-        <v>143.39337719132</v>
+        <v>148.3379764048138</v>
       </c>
       <c r="G31">
         <v>0.249</v>
@@ -4713,37 +4713,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M31">
-        <v>33.81215834171326</v>
+        <v>34.9780948362551</v>
       </c>
       <c r="N31">
-        <v>-24.67615834171325</v>
+        <v>-25.84209483625509</v>
       </c>
       <c r="O31">
-        <v>-5.428754835176916</v>
+        <v>-5.68526086397612</v>
       </c>
       <c r="P31">
-        <v>-19.24740350653634</v>
+        <v>-20.15683397227897</v>
       </c>
       <c r="Q31">
-        <v>-15.96740350653634</v>
+        <v>-16.87683397227897</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1224119575336409</v>
+        <v>0.1235064140698358</v>
       </c>
       <c r="T31">
-        <v>1.769329273294248</v>
+        <v>1.79460540576988</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.0594437060091609</v>
+        <v>0.05746224914218886</v>
       </c>
       <c r="W31">
-        <v>0.2217831741230399</v>
+        <v>0.2222504016522719</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2701986636780042</v>
+        <v>0.261192041555404</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1531296103445666</v>
+        <v>0.1550296103445666</v>
       </c>
       <c r="C32">
-        <v>105.7663503358308</v>
+        <v>96.40605175944702</v>
       </c>
       <c r="D32">
-        <v>253.8553267406446</v>
+        <v>249.4396273777546</v>
       </c>
       <c r="E32">
-        <v>141.0780550554345</v>
+        <v>146.0226542689283</v>
       </c>
       <c r="F32">
-        <v>148.3379764048138</v>
+        <v>153.2825756183076</v>
       </c>
       <c r="G32">
         <v>0.249</v>
@@ -4795,37 +4795,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M32">
-        <v>34.9780948362551</v>
+        <v>36.14403133079693</v>
       </c>
       <c r="N32">
-        <v>-25.84209483625509</v>
+        <v>-27.00803133079692</v>
       </c>
       <c r="O32">
-        <v>-5.68526086397612</v>
+        <v>-5.941766892775323</v>
       </c>
       <c r="P32">
-        <v>-20.15683397227897</v>
+        <v>-21.0662644380216</v>
       </c>
       <c r="Q32">
-        <v>-16.87683397227897</v>
+        <v>-17.7862644380216</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1235064140698358</v>
+        <v>0.1246325939838914</v>
       </c>
       <c r="T32">
-        <v>1.79460540576988</v>
+        <v>1.820614179766545</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.05746224914218886</v>
+        <v>0.05560862820211827</v>
       </c>
       <c r="W32">
-        <v>0.2222504016522719</v>
+        <v>0.2226874854699405</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.261192041555404</v>
+        <v>0.2527664918278103</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1550296103445666</v>
+        <v>0.1569296103445666</v>
       </c>
       <c r="C33">
-        <v>96.40605175944702</v>
+        <v>87.19674496218451</v>
       </c>
       <c r="D33">
-        <v>249.4396273777546</v>
+        <v>245.1749197939859</v>
       </c>
       <c r="E33">
-        <v>146.0226542689283</v>
+        <v>150.9672534824221</v>
       </c>
       <c r="F33">
-        <v>153.2825756183076</v>
+        <v>158.2271748318014</v>
       </c>
       <c r="G33">
         <v>0.249</v>
@@ -4877,37 +4877,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M33">
-        <v>36.14403133079693</v>
+        <v>37.30996782533877</v>
       </c>
       <c r="N33">
-        <v>-27.00803133079692</v>
+        <v>-28.17396782533876</v>
       </c>
       <c r="O33">
-        <v>-5.941766892775323</v>
+        <v>-6.198272921574528</v>
       </c>
       <c r="P33">
-        <v>-21.0662644380216</v>
+        <v>-21.97569490376424</v>
       </c>
       <c r="Q33">
-        <v>-17.7862644380216</v>
+        <v>-18.69569490376423</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1246325939838914</v>
+        <v>0.1257918968365957</v>
       </c>
       <c r="T33">
-        <v>1.820614179766545</v>
+        <v>1.847387917704288</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.05560862820211827</v>
+        <v>0.05387085857080207</v>
       </c>
       <c r="W33">
-        <v>0.2226874854699405</v>
+        <v>0.2230972515490049</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2527664918278103</v>
+        <v>0.2448675389581912</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1569296103445666</v>
+        <v>0.1588296103445666</v>
       </c>
       <c r="C34">
-        <v>87.19674496218451</v>
+        <v>78.13081553983216</v>
       </c>
       <c r="D34">
-        <v>245.1749197939859</v>
+        <v>241.0535895851274</v>
       </c>
       <c r="E34">
-        <v>150.9672534824221</v>
+        <v>155.9118526959159</v>
       </c>
       <c r="F34">
-        <v>158.2271748318014</v>
+        <v>163.1717740452952</v>
       </c>
       <c r="G34">
         <v>0.249</v>
@@ -4959,37 +4959,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M34">
-        <v>37.30996782533877</v>
+        <v>38.47590431988061</v>
       </c>
       <c r="N34">
-        <v>-28.17396782533876</v>
+        <v>-29.3399043198806</v>
       </c>
       <c r="O34">
-        <v>-6.198272921574528</v>
+        <v>-6.454778950373733</v>
       </c>
       <c r="P34">
-        <v>-21.97569490376424</v>
+        <v>-22.88512536950687</v>
       </c>
       <c r="Q34">
-        <v>-18.69569490376423</v>
+        <v>-19.60512536950687</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1257918968365957</v>
+        <v>0.1269858057446046</v>
       </c>
       <c r="T34">
-        <v>1.847387917704288</v>
+        <v>1.874960871699875</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.05387085857080207</v>
+        <v>0.05223840831108079</v>
       </c>
       <c r="W34">
-        <v>0.2230972515490049</v>
+        <v>0.2234821833202472</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2448675389581912</v>
+        <v>0.2374473105049127</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1588296103445666</v>
+        <v>0.1607296103445666</v>
       </c>
       <c r="C35">
-        <v>78.13081553983216</v>
+        <v>69.20115260917595</v>
       </c>
       <c r="D35">
-        <v>241.0535895851274</v>
+        <v>237.068525867965</v>
       </c>
       <c r="E35">
-        <v>155.9118526959159</v>
+        <v>160.8564519094097</v>
       </c>
       <c r="F35">
-        <v>163.1717740452952</v>
+        <v>168.116373258789</v>
       </c>
       <c r="G35">
         <v>0.249</v>
@@ -5041,37 +5041,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M35">
-        <v>38.47590431988061</v>
+        <v>39.64184081442244</v>
       </c>
       <c r="N35">
-        <v>-29.3399043198806</v>
+        <v>-30.50584081442244</v>
       </c>
       <c r="O35">
-        <v>-6.454778950373733</v>
+        <v>-6.711284979172937</v>
       </c>
       <c r="P35">
-        <v>-22.88512536950687</v>
+        <v>-23.7945558352495</v>
       </c>
       <c r="Q35">
-        <v>-19.60512536950687</v>
+        <v>-20.5145558352495</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1269858057446046</v>
+        <v>0.1282158937104319</v>
       </c>
       <c r="T35">
-        <v>1.874960871699875</v>
+        <v>1.903369369755933</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.05223840831108079</v>
+        <v>0.05070198453722546</v>
       </c>
       <c r="W35">
-        <v>0.2234821833202472</v>
+        <v>0.2238444720461223</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2374473105049127</v>
+        <v>0.2304635660782977</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1607296103445666</v>
+        <v>0.1626296103445666</v>
       </c>
       <c r="C36">
-        <v>69.20115260917595</v>
+        <v>60.40110786418825</v>
       </c>
       <c r="D36">
-        <v>237.068525867965</v>
+        <v>233.213080336471</v>
       </c>
       <c r="E36">
-        <v>160.8564519094097</v>
+        <v>165.8010511229035</v>
       </c>
       <c r="F36">
-        <v>168.116373258789</v>
+        <v>173.0609724722828</v>
       </c>
       <c r="G36">
         <v>0.249</v>
@@ -5123,37 +5123,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M36">
-        <v>39.64184081442244</v>
+        <v>40.80777730896428</v>
       </c>
       <c r="N36">
-        <v>-30.50584081442244</v>
+        <v>-31.67177730896427</v>
       </c>
       <c r="O36">
-        <v>-6.711284979172937</v>
+        <v>-6.96779100797214</v>
       </c>
       <c r="P36">
-        <v>-23.7945558352495</v>
+        <v>-24.70398630099213</v>
       </c>
       <c r="Q36">
-        <v>-20.5145558352495</v>
+        <v>-21.42398630099213</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1282158937104319</v>
+        <v>0.1294838305367463</v>
       </c>
       <c r="T36">
-        <v>1.903369369755933</v>
+        <v>1.932651975444486</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.05070198453722546</v>
+        <v>0.04925335640759046</v>
       </c>
       <c r="W36">
-        <v>0.2238444720461223</v>
+        <v>0.2241860585590902</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2304635660782977</v>
+        <v>0.2238788927617749</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1626296103445666</v>
+        <v>0.1645296103445666</v>
       </c>
       <c r="C37">
-        <v>60.40110786418825</v>
+        <v>51.72445856349756</v>
       </c>
       <c r="D37">
-        <v>233.213080336471</v>
+        <v>229.4810302492741</v>
       </c>
       <c r="E37">
-        <v>165.8010511229035</v>
+        <v>170.7456503363973</v>
       </c>
       <c r="F37">
-        <v>173.0609724722828</v>
+        <v>178.0055716857766</v>
       </c>
       <c r="G37">
         <v>0.249</v>
@@ -5205,37 +5205,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M37">
-        <v>40.80777730896428</v>
+        <v>41.97371380350612</v>
       </c>
       <c r="N37">
-        <v>-31.67177730896427</v>
+        <v>-32.83771380350611</v>
       </c>
       <c r="O37">
-        <v>-6.96779100797214</v>
+        <v>-7.224297036771345</v>
       </c>
       <c r="P37">
-        <v>-24.70398630099213</v>
+        <v>-25.61341676673477</v>
       </c>
       <c r="Q37">
-        <v>-21.42398630099213</v>
+        <v>-22.33341676673476</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1294838305367463</v>
+        <v>0.1307913903888829</v>
       </c>
       <c r="T37">
-        <v>1.932651975444486</v>
+        <v>1.962849662560806</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.04925335640759046</v>
+        <v>0.04788520761849072</v>
       </c>
       <c r="W37">
-        <v>0.2241860585590902</v>
+        <v>0.2245086680435599</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2238788927617749</v>
+        <v>0.2176600346295033</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1645296103445666</v>
+        <v>0.1664296103445666</v>
       </c>
       <c r="C38">
-        <v>51.72445856349759</v>
+        <v>43.1653740156967</v>
       </c>
       <c r="D38">
-        <v>229.4810302492741</v>
+        <v>225.8665449149671</v>
       </c>
       <c r="E38">
-        <v>170.7456503363972</v>
+        <v>175.690249549891</v>
       </c>
       <c r="F38">
-        <v>178.0055716857765</v>
+        <v>182.9501708992703</v>
       </c>
       <c r="G38">
         <v>0.249</v>
@@ -5287,37 +5287,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M38">
-        <v>41.97371380350611</v>
+        <v>43.13965029804795</v>
       </c>
       <c r="N38">
-        <v>-32.83771380350611</v>
+        <v>-34.00365029804794</v>
       </c>
       <c r="O38">
-        <v>-7.224297036771343</v>
+        <v>-7.480803065570548</v>
       </c>
       <c r="P38">
-        <v>-25.61341676673476</v>
+        <v>-26.5228472324774</v>
       </c>
       <c r="Q38">
-        <v>-22.33341676673476</v>
+        <v>-23.24284723247739</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1307913903888829</v>
+        <v>0.1321404600775953</v>
       </c>
       <c r="T38">
-        <v>1.962849662560806</v>
+        <v>1.994006006410977</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.04788520761849073</v>
+        <v>0.04659101281799098</v>
       </c>
       <c r="W38">
-        <v>0.2245086680435599</v>
+        <v>0.2248138391775177</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2176600346295033</v>
+        <v>0.2117773309908682</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1664296103445666</v>
+        <v>0.1683296103445666</v>
       </c>
       <c r="C39">
-        <v>43.1653740156967</v>
+        <v>34.71838518281515</v>
       </c>
       <c r="D39">
-        <v>225.8665449149671</v>
+        <v>222.3641552955793</v>
       </c>
       <c r="E39">
-        <v>175.690249549891</v>
+        <v>180.6348487633848</v>
       </c>
       <c r="F39">
-        <v>182.9501708992703</v>
+        <v>187.8947701127641</v>
       </c>
       <c r="G39">
         <v>0.249</v>
@@ -5369,37 +5369,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M39">
-        <v>43.13965029804795</v>
+        <v>44.30558679258979</v>
       </c>
       <c r="N39">
-        <v>-34.00365029804794</v>
+        <v>-35.16958679258978</v>
       </c>
       <c r="O39">
-        <v>-7.480803065570548</v>
+        <v>-7.737309094369753</v>
       </c>
       <c r="P39">
-        <v>-26.5228472324774</v>
+        <v>-27.43227769822003</v>
       </c>
       <c r="Q39">
-        <v>-23.24284723247739</v>
+        <v>-24.15227769822003</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1321404600775953</v>
+        <v>0.133533048143363</v>
       </c>
       <c r="T39">
-        <v>1.994006006410977</v>
+        <v>2.026167393611154</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.04659101281799098</v>
+        <v>0.04536493353330701</v>
       </c>
       <c r="W39">
-        <v>0.2248138391775177</v>
+        <v>0.2251029486728462</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2117773309908682</v>
+        <v>0.2062042433332137</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1683296103445666</v>
+        <v>0.1702296103445666</v>
       </c>
       <c r="C40">
-        <v>34.71838518281515</v>
+        <v>26.37835706866289</v>
       </c>
       <c r="D40">
-        <v>222.3641552955793</v>
+        <v>218.9687263949208</v>
       </c>
       <c r="E40">
-        <v>180.6348487633848</v>
+        <v>185.5794479768786</v>
       </c>
       <c r="F40">
-        <v>187.8947701127641</v>
+        <v>192.839369326258</v>
       </c>
       <c r="G40">
         <v>0.249</v>
@@ -5451,37 +5451,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M40">
-        <v>44.30558679258979</v>
+        <v>45.47152328713162</v>
       </c>
       <c r="N40">
-        <v>-35.16958679258978</v>
+        <v>-36.33552328713162</v>
       </c>
       <c r="O40">
-        <v>-7.737309094369753</v>
+        <v>-7.993815123168956</v>
       </c>
       <c r="P40">
-        <v>-27.43227769822003</v>
+        <v>-28.34170816396266</v>
       </c>
       <c r="Q40">
-        <v>-24.15227769822003</v>
+        <v>-25.06170816396266</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.133533048143363</v>
+        <v>0.1349712948342378</v>
       </c>
       <c r="T40">
-        <v>2.026167393611154</v>
+        <v>2.059383252522813</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.04536493353330701</v>
+        <v>0.04420173010937605</v>
       </c>
       <c r="W40">
-        <v>0.2251029486728462</v>
+        <v>0.2253772320402092</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2062042433332137</v>
+        <v>0.2009169550426184</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1702296103445666</v>
+        <v>0.1721296103445666</v>
       </c>
       <c r="C41">
-        <v>26.37835706866289</v>
+        <v>18.14046359885347</v>
       </c>
       <c r="D41">
-        <v>218.9687263949208</v>
+        <v>215.6754321386052</v>
       </c>
       <c r="E41">
-        <v>185.5794479768786</v>
+        <v>190.5240471903724</v>
       </c>
       <c r="F41">
-        <v>192.839369326258</v>
+        <v>197.7839685397518</v>
       </c>
       <c r="G41">
         <v>0.249</v>
@@ -5533,37 +5533,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M41">
-        <v>45.47152328713162</v>
+        <v>46.63745978167346</v>
       </c>
       <c r="N41">
-        <v>-36.33552328713162</v>
+        <v>-37.50145978167346</v>
       </c>
       <c r="O41">
-        <v>-7.993815123168956</v>
+        <v>-8.250321151968162</v>
       </c>
       <c r="P41">
-        <v>-28.34170816396266</v>
+        <v>-29.2511386297053</v>
       </c>
       <c r="Q41">
-        <v>-25.06170816396266</v>
+        <v>-25.9711386297053</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1349712948342378</v>
+        <v>0.1364574830814751</v>
       </c>
       <c r="T41">
-        <v>2.059383252522813</v>
+        <v>2.093706306731526</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.04420173010937605</v>
+        <v>0.04309668685664165</v>
       </c>
       <c r="W41">
-        <v>0.2253772320402092</v>
+        <v>0.2256378012392039</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2009169550426184</v>
+        <v>0.195894031166553</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1721296103445666</v>
+        <v>0.1740296103445666</v>
       </c>
       <c r="C42">
-        <v>18.14046359885347</v>
+        <v>10.00016473406842</v>
       </c>
       <c r="D42">
-        <v>215.6754321386052</v>
+        <v>212.479732487314</v>
       </c>
       <c r="E42">
-        <v>190.5240471903724</v>
+        <v>195.4686464038662</v>
       </c>
       <c r="F42">
-        <v>197.7839685397518</v>
+        <v>202.7285677532455</v>
       </c>
       <c r="G42">
         <v>0.249</v>
@@ -5615,37 +5615,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M42">
-        <v>46.63745978167346</v>
+        <v>47.8033962762153</v>
       </c>
       <c r="N42">
-        <v>-37.50145978167346</v>
+        <v>-38.66739627621529</v>
       </c>
       <c r="O42">
-        <v>-8.250321151968162</v>
+        <v>-8.506827180767365</v>
       </c>
       <c r="P42">
-        <v>-29.2511386297053</v>
+        <v>-30.16056909544793</v>
       </c>
       <c r="Q42">
-        <v>-25.9711386297053</v>
+        <v>-26.88056909544792</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1364574830814751</v>
+        <v>0.1379940505913306</v>
       </c>
       <c r="T42">
-        <v>2.093706306731526</v>
+        <v>2.129192854303247</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.04309668685664165</v>
+        <v>0.04204554815282113</v>
       </c>
       <c r="W42">
-        <v>0.2256378012392039</v>
+        <v>0.2258856597455648</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.195894031166553</v>
+        <v>0.1911161279673688</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1740296103445666</v>
+        <v>0.1759296103445666</v>
       </c>
       <c r="C43">
-        <v>10.00016473406842</v>
+        <v>1.953185588313858</v>
       </c>
       <c r="D43">
-        <v>212.479732487314</v>
+        <v>209.3773525550532</v>
       </c>
       <c r="E43">
-        <v>195.4686464038662</v>
+        <v>200.41324561736</v>
       </c>
       <c r="F43">
-        <v>202.7285677532455</v>
+        <v>207.6731669667393</v>
       </c>
       <c r="G43">
         <v>0.249</v>
@@ -5697,37 +5697,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M43">
-        <v>47.8033962762153</v>
+        <v>48.96933277075713</v>
       </c>
       <c r="N43">
-        <v>-38.66739627621529</v>
+        <v>-39.83333277075713</v>
       </c>
       <c r="O43">
-        <v>-8.506827180767365</v>
+        <v>-8.76333320956657</v>
       </c>
       <c r="P43">
-        <v>-30.16056909544793</v>
+        <v>-31.06999956119056</v>
       </c>
       <c r="Q43">
-        <v>-26.88056909544792</v>
+        <v>-27.78999956119056</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1379940505913306</v>
+        <v>0.1395836031877329</v>
       </c>
       <c r="T43">
-        <v>2.129192854303247</v>
+        <v>2.165903075929165</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.04204554815282113</v>
+        <v>0.04104446367299205</v>
       </c>
       <c r="W43">
-        <v>0.2258856597455648</v>
+        <v>0.2261217154659085</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1911161279673688</v>
+        <v>0.1865657439681457</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1759296103445666</v>
+        <v>0.1778296103445666</v>
       </c>
       <c r="C44">
-        <v>1.953185588313886</v>
+        <v>-6.004502649803982</v>
       </c>
       <c r="D44">
-        <v>209.3773525550532</v>
+        <v>206.3642635304291</v>
       </c>
       <c r="E44">
-        <v>200.41324561736</v>
+        <v>205.3578448308538</v>
       </c>
       <c r="F44">
-        <v>207.6731669667393</v>
+        <v>212.6177661802331</v>
       </c>
       <c r="G44">
         <v>0.249</v>
@@ -5779,37 +5779,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M44">
-        <v>48.96933277075713</v>
+        <v>50.13526926529897</v>
       </c>
       <c r="N44">
-        <v>-39.83333277075712</v>
+        <v>-40.99926926529896</v>
       </c>
       <c r="O44">
-        <v>-8.763333209566568</v>
+        <v>-9.019839238365773</v>
       </c>
       <c r="P44">
-        <v>-31.06999956119056</v>
+        <v>-31.97943002693319</v>
       </c>
       <c r="Q44">
-        <v>-27.78999956119056</v>
+        <v>-28.69943002693319</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1395836031877328</v>
+        <v>0.1412289295594475</v>
       </c>
       <c r="T44">
-        <v>2.165903075929165</v>
+        <v>2.20390137550687</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.04104446367299205</v>
+        <v>0.04008994126199224</v>
       </c>
       <c r="W44">
-        <v>0.2261217154659085</v>
+        <v>0.2263467918504222</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1865657439681457</v>
+        <v>0.1822270057363283</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1778296103445666</v>
+        <v>0.1797296103445666</v>
       </c>
       <c r="C45">
-        <v>-6.004502649803982</v>
+        <v>-13.8767001718351</v>
       </c>
       <c r="D45">
-        <v>206.3642635304291</v>
+        <v>203.4366652218918</v>
       </c>
       <c r="E45">
-        <v>205.3578448308538</v>
+        <v>210.3024440443476</v>
       </c>
       <c r="F45">
-        <v>212.6177661802331</v>
+        <v>217.5623653937269</v>
       </c>
       <c r="G45">
         <v>0.249</v>
@@ -5861,37 +5861,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M45">
-        <v>50.13526926529897</v>
+        <v>51.3012057598408</v>
       </c>
       <c r="N45">
-        <v>-40.99926926529896</v>
+        <v>-42.1652057598408</v>
       </c>
       <c r="O45">
-        <v>-9.019839238365773</v>
+        <v>-9.276345267164977</v>
       </c>
       <c r="P45">
-        <v>-31.97943002693319</v>
+        <v>-32.88886049267582</v>
       </c>
       <c r="Q45">
-        <v>-28.69943002693319</v>
+        <v>-29.60886049267582</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1412289295594475</v>
+        <v>0.1429330175872947</v>
       </c>
       <c r="T45">
-        <v>2.20390137550687</v>
+        <v>2.24325675721235</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.04008994126199224</v>
+        <v>0.03917880623331059</v>
       </c>
       <c r="W45">
-        <v>0.2263467918504222</v>
+        <v>0.2265616374901854</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1822270057363283</v>
+        <v>0.1780854828786845</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1797296103445666</v>
+        <v>0.1816296103445666</v>
       </c>
       <c r="C46">
-        <v>-13.8767001718351</v>
+        <v>-21.66699453928729</v>
       </c>
       <c r="D46">
-        <v>203.4366652218918</v>
+        <v>200.5909700679334</v>
       </c>
       <c r="E46">
-        <v>210.3024440443476</v>
+        <v>215.2470432578414</v>
       </c>
       <c r="F46">
-        <v>217.5623653937269</v>
+        <v>222.5069646072207</v>
       </c>
       <c r="G46">
         <v>0.249</v>
@@ -5943,37 +5943,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M46">
-        <v>51.3012057598408</v>
+        <v>52.46714225438264</v>
       </c>
       <c r="N46">
-        <v>-42.1652057598408</v>
+        <v>-43.33114225438264</v>
       </c>
       <c r="O46">
-        <v>-9.276345267164977</v>
+        <v>-9.53285129596418</v>
       </c>
       <c r="P46">
-        <v>-32.88886049267582</v>
+        <v>-33.79829095841846</v>
       </c>
       <c r="Q46">
-        <v>-29.60886049267582</v>
+        <v>-30.51829095841846</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1429330175872947</v>
+        <v>0.1446990724525183</v>
       </c>
       <c r="T46">
-        <v>2.24325675721235</v>
+        <v>2.284043243707119</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.03917880623331059</v>
+        <v>0.03830816609479258</v>
       </c>
       <c r="W46">
-        <v>0.2265616374901854</v>
+        <v>0.2267669344348479</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1780854828786845</v>
+        <v>0.1741280277036027</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1816296103445666</v>
+        <v>0.1835296103445666</v>
       </c>
       <c r="C47">
-        <v>-21.66699453928729</v>
+        <v>-29.37877534993794</v>
       </c>
       <c r="D47">
-        <v>200.5909700679334</v>
+        <v>197.8237884707766</v>
       </c>
       <c r="E47">
-        <v>215.2470432578414</v>
+        <v>220.1916424713352</v>
       </c>
       <c r="F47">
-        <v>222.5069646072207</v>
+        <v>227.4515638207145</v>
       </c>
       <c r="G47">
         <v>0.249</v>
@@ -6025,37 +6025,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M47">
-        <v>52.46714225438264</v>
+        <v>53.63307874892448</v>
       </c>
       <c r="N47">
-        <v>-43.33114225438264</v>
+        <v>-44.49707874892448</v>
       </c>
       <c r="O47">
-        <v>-9.53285129596418</v>
+        <v>-9.789357324763385</v>
       </c>
       <c r="P47">
-        <v>-33.79829095841846</v>
+        <v>-34.70772142416109</v>
       </c>
       <c r="Q47">
-        <v>-30.51829095841846</v>
+        <v>-31.42772142416109</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1446990724525183</v>
+        <v>0.1465305367571945</v>
       </c>
       <c r="T47">
-        <v>2.284043243707119</v>
+        <v>2.326340340812807</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.03830816609479258</v>
+        <v>0.03747537987534057</v>
       </c>
       <c r="W47">
-        <v>0.2267669344348479</v>
+        <v>0.2269633054253947</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1741280277036027</v>
+        <v>0.1703426357970026</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1835296103445666</v>
+        <v>0.1854296103445666</v>
       </c>
       <c r="C48">
-        <v>-29.37877534993794</v>
+        <v>-37.01524770672094</v>
       </c>
       <c r="D48">
-        <v>197.8237884707766</v>
+        <v>195.1319153274873</v>
       </c>
       <c r="E48">
-        <v>220.1916424713352</v>
+        <v>225.136241684829</v>
       </c>
       <c r="F48">
-        <v>227.4515638207145</v>
+        <v>232.3961630342083</v>
       </c>
       <c r="G48">
         <v>0.249</v>
@@ -6107,37 +6107,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M48">
-        <v>53.63307874892448</v>
+        <v>54.79901524346631</v>
       </c>
       <c r="N48">
-        <v>-44.49707874892448</v>
+        <v>-45.66301524346631</v>
       </c>
       <c r="O48">
-        <v>-9.789357324763385</v>
+        <v>-10.04586335356259</v>
       </c>
       <c r="P48">
-        <v>-34.70772142416109</v>
+        <v>-35.61715188990372</v>
       </c>
       <c r="Q48">
-        <v>-31.42772142416109</v>
+        <v>-32.33715188990372</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1465305367571945</v>
+        <v>0.1484311129224246</v>
       </c>
       <c r="T48">
-        <v>2.326340340812807</v>
+        <v>2.370233554790408</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.03747537987534057</v>
+        <v>0.0366780313673546</v>
       </c>
       <c r="W48">
-        <v>0.2269633054253947</v>
+        <v>0.2271513202035778</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1703426357970026</v>
+        <v>0.1667183243970664</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1854296103445666</v>
+        <v>0.1873296103445666</v>
       </c>
       <c r="C49">
-        <v>-37.01524770672094</v>
+        <v>-44.57944460171475</v>
       </c>
       <c r="D49">
-        <v>195.1319153274873</v>
+        <v>192.5123176459873</v>
       </c>
       <c r="E49">
-        <v>225.136241684829</v>
+        <v>230.0808408983228</v>
       </c>
       <c r="F49">
-        <v>232.3961630342083</v>
+        <v>237.3407622477021</v>
       </c>
       <c r="G49">
         <v>0.249</v>
@@ -6189,37 +6189,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M49">
-        <v>54.79901524346631</v>
+        <v>55.96495173800815</v>
       </c>
       <c r="N49">
-        <v>-45.66301524346631</v>
+        <v>-46.82895173800815</v>
       </c>
       <c r="O49">
-        <v>-10.04586335356259</v>
+        <v>-10.30236938236179</v>
       </c>
       <c r="P49">
-        <v>-35.61715188990372</v>
+        <v>-36.52658235564635</v>
       </c>
       <c r="Q49">
-        <v>-32.33715188990372</v>
+        <v>-33.24658235564635</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1484311129224246</v>
+        <v>0.1504047881709328</v>
       </c>
       <c r="T49">
-        <v>2.370233554790408</v>
+        <v>2.415814969305608</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.0366780313673546</v>
+        <v>0.03591390571386804</v>
       </c>
       <c r="W49">
-        <v>0.2271513202035778</v>
+        <v>0.2273315010326699</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1667183243970664</v>
+        <v>0.1632450259721275</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1873296103445666</v>
+        <v>0.1892296103445666</v>
       </c>
       <c r="C50">
-        <v>-44.57944460171473</v>
+        <v>-52.0742383158327</v>
       </c>
       <c r="D50">
-        <v>192.5123176459873</v>
+        <v>189.9621231453632</v>
       </c>
       <c r="E50">
-        <v>230.0808408983227</v>
+        <v>235.0254401118166</v>
       </c>
       <c r="F50">
-        <v>237.3407622477021</v>
+        <v>242.2853614611959</v>
       </c>
       <c r="G50">
         <v>0.249</v>
@@ -6271,37 +6271,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M50">
-        <v>55.96495173800815</v>
+        <v>57.13088823254999</v>
       </c>
       <c r="N50">
-        <v>-46.82895173800814</v>
+        <v>-47.99488823254998</v>
       </c>
       <c r="O50">
-        <v>-10.30236938236179</v>
+        <v>-10.558875411161</v>
       </c>
       <c r="P50">
-        <v>-36.52658235564635</v>
+        <v>-37.43601282138899</v>
       </c>
       <c r="Q50">
-        <v>-33.24658235564635</v>
+        <v>-34.15601282138898</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1504047881709328</v>
+        <v>0.1524558624487942</v>
       </c>
       <c r="T50">
-        <v>2.415814969305607</v>
+        <v>2.463183890272384</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.03591390571386804</v>
+        <v>0.03518096886256462</v>
       </c>
       <c r="W50">
-        <v>0.2273315010326699</v>
+        <v>0.2275043275422073</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1632450259721275</v>
+        <v>0.1599134948298392</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1892296103445666</v>
+        <v>0.1911296103445666</v>
       </c>
       <c r="C51">
-        <v>-52.0742383158327</v>
+        <v>-59.50235092429432</v>
       </c>
       <c r="D51">
-        <v>189.9621231453632</v>
+        <v>187.4786097503953</v>
       </c>
       <c r="E51">
-        <v>235.0254401118166</v>
+        <v>239.9700393253104</v>
       </c>
       <c r="F51">
-        <v>242.2853614611959</v>
+        <v>247.2299606746897</v>
       </c>
       <c r="G51">
         <v>0.249</v>
@@ -6353,37 +6353,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M51">
-        <v>57.13088823254999</v>
+        <v>58.29682472709182</v>
       </c>
       <c r="N51">
-        <v>-47.99488823254998</v>
+        <v>-49.16082472709182</v>
       </c>
       <c r="O51">
-        <v>-10.558875411161</v>
+        <v>-10.8153814399602</v>
       </c>
       <c r="P51">
-        <v>-37.43601282138899</v>
+        <v>-38.34544328713162</v>
       </c>
       <c r="Q51">
-        <v>-34.15601282138898</v>
+        <v>-35.06544328713162</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1524558624487942</v>
+        <v>0.1545889796977701</v>
       </c>
       <c r="T51">
-        <v>2.463183890272384</v>
+        <v>2.512447568077832</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.03518096886256462</v>
+        <v>0.03447734948531332</v>
       </c>
       <c r="W51">
-        <v>0.2275043275422073</v>
+        <v>0.2276702409913631</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1599134948298392</v>
+        <v>0.1567152249332424</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1911296103445666</v>
+        <v>0.1930296103445666</v>
       </c>
       <c r="C52">
-        <v>-59.50235092429432</v>
+        <v>-66.86636398865758</v>
       </c>
       <c r="D52">
-        <v>187.4786097503953</v>
+        <v>185.0591958995259</v>
       </c>
       <c r="E52">
-        <v>239.9700393253104</v>
+        <v>244.9146385388042</v>
       </c>
       <c r="F52">
-        <v>247.2299606746897</v>
+        <v>252.1745598881835</v>
       </c>
       <c r="G52">
         <v>0.249</v>
@@ -6435,37 +6435,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M52">
-        <v>58.29682472709182</v>
+        <v>59.46276122163366</v>
       </c>
       <c r="N52">
-        <v>-49.16082472709182</v>
+        <v>-50.32676122163366</v>
       </c>
       <c r="O52">
-        <v>-10.8153814399602</v>
+        <v>-11.0718874687594</v>
       </c>
       <c r="P52">
-        <v>-38.34544328713162</v>
+        <v>-39.25487375287425</v>
       </c>
       <c r="Q52">
-        <v>-35.06544328713162</v>
+        <v>-35.97487375287425</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1545889796977701</v>
+        <v>0.1568091629569083</v>
       </c>
       <c r="T52">
-        <v>2.512447568077832</v>
+        <v>2.563722008242686</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.03447734948531332</v>
+        <v>0.03380132302481698</v>
       </c>
       <c r="W52">
-        <v>0.2276702409913631</v>
+        <v>0.2278296480307482</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1567152249332424</v>
+        <v>0.1536423773855318</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1930296103445666</v>
+        <v>0.1949296103445666</v>
       </c>
       <c r="C53">
-        <v>-66.86636398865758</v>
+        <v>-74.16872750795682</v>
       </c>
       <c r="D53">
-        <v>185.0591958995259</v>
+        <v>182.7014315937205</v>
       </c>
       <c r="E53">
-        <v>244.9146385388042</v>
+        <v>249.859237752298</v>
       </c>
       <c r="F53">
-        <v>252.1745598881835</v>
+        <v>257.1191591016773</v>
       </c>
       <c r="G53">
         <v>0.249</v>
@@ -6517,37 +6517,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M53">
-        <v>59.46276122163366</v>
+        <v>60.6286977161755</v>
       </c>
       <c r="N53">
-        <v>-50.32676122163366</v>
+        <v>-51.4926977161755</v>
       </c>
       <c r="O53">
-        <v>-11.0718874687594</v>
+        <v>-11.32839349755861</v>
       </c>
       <c r="P53">
-        <v>-39.25487375287425</v>
+        <v>-40.16430421861689</v>
       </c>
       <c r="Q53">
-        <v>-35.97487375287425</v>
+        <v>-36.88430421861689</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1568091629569083</v>
+        <v>0.1591218538518439</v>
       </c>
       <c r="T53">
-        <v>2.563722008242686</v>
+        <v>2.617132883414409</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03380132302481698</v>
+        <v>0.03315129758203204</v>
       </c>
       <c r="W53">
-        <v>0.2278296480307482</v>
+        <v>0.2279829240301569</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1536423773855318</v>
+        <v>0.1506877162819639</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1949296103445666</v>
+        <v>0.1968296103445666</v>
       </c>
       <c r="C54">
-        <v>-74.16872750795682</v>
+        <v>-81.41176819419303</v>
       </c>
       <c r="D54">
-        <v>182.7014315937205</v>
+        <v>180.402990120978</v>
       </c>
       <c r="E54">
-        <v>249.859237752298</v>
+        <v>254.8038369657918</v>
       </c>
       <c r="F54">
-        <v>257.1191591016773</v>
+        <v>262.0637583151711</v>
       </c>
       <c r="G54">
         <v>0.249</v>
@@ -6599,37 +6599,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M54">
-        <v>60.6286977161755</v>
+        <v>61.79463421071734</v>
       </c>
       <c r="N54">
-        <v>-51.4926977161755</v>
+        <v>-52.65863421071734</v>
       </c>
       <c r="O54">
-        <v>-11.32839349755861</v>
+        <v>-11.58489952635781</v>
       </c>
       <c r="P54">
-        <v>-40.16430421861689</v>
+        <v>-41.07373468435952</v>
       </c>
       <c r="Q54">
-        <v>-36.88430421861689</v>
+        <v>-37.79373468435952</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1591218538518439</v>
+        <v>0.1615329571252874</v>
       </c>
       <c r="T54">
-        <v>2.617132883414409</v>
+        <v>2.672816561784928</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03315129758203204</v>
+        <v>0.03252580140123898</v>
       </c>
       <c r="W54">
-        <v>0.2279829240301569</v>
+        <v>0.2281304160295879</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1506877162819639</v>
+        <v>0.1478445518238136</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1968296103445666</v>
+        <v>0.1987296103445666</v>
       </c>
       <c r="C55">
-        <v>-81.41176819419303</v>
+        <v>-88.5976971309338</v>
       </c>
       <c r="D55">
-        <v>180.402990120978</v>
+        <v>178.1616603977311</v>
       </c>
       <c r="E55">
-        <v>254.8038369657918</v>
+        <v>259.7484361792855</v>
       </c>
       <c r="F55">
-        <v>262.0637583151711</v>
+        <v>267.0083575286649</v>
       </c>
       <c r="G55">
         <v>0.249</v>
@@ -6681,37 +6681,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M55">
-        <v>61.79463421071734</v>
+        <v>62.96057070525918</v>
       </c>
       <c r="N55">
-        <v>-52.65863421071734</v>
+        <v>-53.82457070525918</v>
       </c>
       <c r="O55">
-        <v>-11.58489952635781</v>
+        <v>-11.84140555515702</v>
       </c>
       <c r="P55">
-        <v>-41.07373468435952</v>
+        <v>-41.98316515010216</v>
       </c>
       <c r="Q55">
-        <v>-37.79373468435952</v>
+        <v>-38.70316515010216</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1615329571252874</v>
+        <v>0.1640488909758371</v>
       </c>
       <c r="T55">
-        <v>2.672816561784928</v>
+        <v>2.730921269649818</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03252580140123898</v>
+        <v>0.03192347174566048</v>
       </c>
       <c r="W55">
-        <v>0.2281304160295879</v>
+        <v>0.2282724453623733</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1478445518238136</v>
+        <v>0.1451066897530022</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1987296103445666</v>
+        <v>0.2006296103445666</v>
       </c>
       <c r="C56">
-        <v>-88.5976971309338</v>
+        <v>-95.72861686801704</v>
       </c>
       <c r="D56">
-        <v>178.1616603977311</v>
+        <v>175.9753398741416</v>
       </c>
       <c r="E56">
-        <v>259.7484361792855</v>
+        <v>264.6930353927793</v>
       </c>
       <c r="F56">
-        <v>267.0083575286649</v>
+        <v>271.9529567421587</v>
       </c>
       <c r="G56">
         <v>0.249</v>
@@ -6763,37 +6763,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M56">
-        <v>62.96057070525918</v>
+        <v>64.12650719980101</v>
       </c>
       <c r="N56">
-        <v>-53.82457070525918</v>
+        <v>-54.99050719980101</v>
       </c>
       <c r="O56">
-        <v>-11.84140555515702</v>
+        <v>-12.09791158395622</v>
       </c>
       <c r="P56">
-        <v>-41.98316515010216</v>
+        <v>-42.89259561584478</v>
       </c>
       <c r="Q56">
-        <v>-38.70316515010216</v>
+        <v>-39.61259561584478</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1640488909758371</v>
+        <v>0.1666766441086335</v>
       </c>
       <c r="T56">
-        <v>2.730921269649818</v>
+        <v>2.791608408975369</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03192347174566048</v>
+        <v>0.03134304498664847</v>
       </c>
       <c r="W56">
-        <v>0.2282724453623733</v>
+        <v>0.2284093099921483</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1451066897530022</v>
+        <v>0.1424683863029477</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2006296103445666</v>
+        <v>0.2025296103445666</v>
       </c>
       <c r="C57">
-        <v>-95.72861686801704</v>
+        <v>-102.8065280002083</v>
       </c>
       <c r="D57">
-        <v>175.9753398741416</v>
+        <v>173.8420279554442</v>
       </c>
       <c r="E57">
-        <v>264.6930353927793</v>
+        <v>269.6376346062731</v>
       </c>
       <c r="F57">
-        <v>271.9529567421587</v>
+        <v>276.8975559556525</v>
       </c>
       <c r="G57">
         <v>0.249</v>
@@ -6845,37 +6845,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M57">
-        <v>64.12650719980101</v>
+        <v>65.29244369434285</v>
       </c>
       <c r="N57">
-        <v>-54.99050719980101</v>
+        <v>-56.15644369434285</v>
       </c>
       <c r="O57">
-        <v>-12.09791158395622</v>
+        <v>-12.35441761275543</v>
       </c>
       <c r="P57">
-        <v>-42.89259561584478</v>
+        <v>-43.80202608158742</v>
       </c>
       <c r="Q57">
-        <v>-39.61259561584478</v>
+        <v>-40.52202608158742</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1666766441086335</v>
+        <v>0.1694238405656479</v>
       </c>
       <c r="T57">
-        <v>2.791608408975369</v>
+        <v>2.8550540546339</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03134304498664847</v>
+        <v>0.03078334775474403</v>
       </c>
       <c r="W57">
-        <v>0.2284093099921483</v>
+        <v>0.2285412865994314</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1424683863029477</v>
+        <v>0.1399243079761092</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2025296103445666</v>
+        <v>0.2044296103445666</v>
       </c>
       <c r="C58">
-        <v>-102.8065280002083</v>
+        <v>-109.8333352730795</v>
       </c>
       <c r="D58">
-        <v>173.8420279554442</v>
+        <v>171.7598198960668</v>
       </c>
       <c r="E58">
-        <v>269.6376346062731</v>
+        <v>274.5822338197669</v>
       </c>
       <c r="F58">
-        <v>276.8975559556525</v>
+        <v>281.8421551691462</v>
       </c>
       <c r="G58">
         <v>0.249</v>
@@ -6927,37 +6927,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M58">
-        <v>65.29244369434285</v>
+        <v>66.45838018888469</v>
       </c>
       <c r="N58">
-        <v>-56.15644369434285</v>
+        <v>-57.32238018888469</v>
       </c>
       <c r="O58">
-        <v>-12.35441761275543</v>
+        <v>-12.61092364155463</v>
       </c>
       <c r="P58">
-        <v>-43.80202608158742</v>
+        <v>-44.71145654733006</v>
       </c>
       <c r="Q58">
-        <v>-40.52202608158742</v>
+        <v>-41.43145654733006</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1694238405656479</v>
+        <v>0.1722988136020583</v>
       </c>
       <c r="T58">
-        <v>2.8550540546339</v>
+        <v>2.921450660555619</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03078334775474403</v>
+        <v>0.03024328902220466</v>
       </c>
       <c r="W58">
-        <v>0.2285412865994314</v>
+        <v>0.2286686324485642</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1399243079761092</v>
+        <v>0.1374694955554757</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2044296103445666</v>
+        <v>0.2063296103445666</v>
       </c>
       <c r="C59">
-        <v>-109.8333352730795</v>
+        <v>-116.8108532552792</v>
       </c>
       <c r="D59">
-        <v>171.7598198960668</v>
+        <v>169.7269011273608</v>
       </c>
       <c r="E59">
-        <v>274.5822338197669</v>
+        <v>279.5268330332607</v>
       </c>
       <c r="F59">
-        <v>281.8421551691462</v>
+        <v>286.78675438264</v>
       </c>
       <c r="G59">
         <v>0.249</v>
@@ -7009,37 +7009,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M59">
-        <v>66.45838018888469</v>
+        <v>67.62431668342651</v>
       </c>
       <c r="N59">
-        <v>-57.32238018888469</v>
+        <v>-58.48831668342651</v>
       </c>
       <c r="O59">
-        <v>-12.61092364155463</v>
+        <v>-12.86742967035383</v>
       </c>
       <c r="P59">
-        <v>-44.71145654733006</v>
+        <v>-45.62088701307268</v>
       </c>
       <c r="Q59">
-        <v>-41.43145654733006</v>
+        <v>-42.34088701307267</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1722988136020583</v>
+        <v>0.175310690116393</v>
       </c>
       <c r="T59">
-        <v>2.921450660555619</v>
+        <v>2.991009009616467</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03024328902220466</v>
+        <v>0.02972185300458045</v>
       </c>
       <c r="W59">
-        <v>0.2286686324485642</v>
+        <v>0.2287915870615199</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1374694955554757</v>
+        <v>0.135099331839002</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2063296103445666</v>
+        <v>0.2082296103445666</v>
       </c>
       <c r="C60">
-        <v>-116.8108532552791</v>
+        <v>-123.7408116126993</v>
       </c>
       <c r="D60">
-        <v>169.7269011273609</v>
+        <v>167.7415419834344</v>
       </c>
       <c r="E60">
-        <v>279.5268330332606</v>
+        <v>284.4714322467544</v>
       </c>
       <c r="F60">
-        <v>286.78675438264</v>
+        <v>291.7313535961338</v>
       </c>
       <c r="G60">
         <v>0.249</v>
@@ -7091,37 +7091,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M60">
-        <v>67.62431668342651</v>
+        <v>68.79025317796835</v>
       </c>
       <c r="N60">
-        <v>-58.48831668342651</v>
+        <v>-59.65425317796835</v>
       </c>
       <c r="O60">
-        <v>-12.86742967035383</v>
+        <v>-13.12393569915304</v>
       </c>
       <c r="P60">
-        <v>-45.62088701307268</v>
+        <v>-46.53031747881531</v>
       </c>
       <c r="Q60">
-        <v>-42.34088701307267</v>
+        <v>-43.25031747881531</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.175310690116393</v>
+        <v>0.178469487436305</v>
       </c>
       <c r="T60">
-        <v>2.991009009616466</v>
+        <v>3.063960448875404</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02972185300458045</v>
+        <v>0.02921809278416383</v>
       </c>
       <c r="W60">
-        <v>0.2287915870615199</v>
+        <v>0.2289103737214942</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.135099331839002</v>
+        <v>0.1328095126552902</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2082296103445666</v>
+        <v>0.2101296103445666</v>
       </c>
       <c r="C61">
-        <v>-123.7408116126993</v>
+        <v>-130.6248600167575</v>
       </c>
       <c r="D61">
-        <v>167.7415419834344</v>
+        <v>165.8020927928701</v>
       </c>
       <c r="E61">
-        <v>284.4714322467544</v>
+        <v>289.4160314602482</v>
       </c>
       <c r="F61">
-        <v>291.7313535961338</v>
+        <v>296.6759528096276</v>
       </c>
       <c r="G61">
         <v>0.249</v>
@@ -7173,37 +7173,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M61">
-        <v>68.79025317796835</v>
+        <v>69.95618967251019</v>
       </c>
       <c r="N61">
-        <v>-59.65425317796835</v>
+        <v>-60.82018967251019</v>
       </c>
       <c r="O61">
-        <v>-13.12393569915304</v>
+        <v>-13.38044172795224</v>
       </c>
       <c r="P61">
-        <v>-46.53031747881531</v>
+        <v>-47.43974794455795</v>
       </c>
       <c r="Q61">
-        <v>-43.25031747881531</v>
+        <v>-44.15974794455795</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.178469487436305</v>
+        <v>0.1817862246222126</v>
       </c>
       <c r="T61">
-        <v>3.063960448875404</v>
+        <v>3.140559460097289</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02921809278416383</v>
+        <v>0.02873112457109443</v>
       </c>
       <c r="W61">
-        <v>0.2289103737214942</v>
+        <v>0.2290252008261359</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1328095126552902</v>
+        <v>0.130596020777702</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2101296103445666</v>
+        <v>0.2120296103445666</v>
       </c>
       <c r="C62">
-        <v>-130.6248600167575</v>
+        <v>-137.4645727160705</v>
       </c>
       <c r="D62">
-        <v>165.8020927928701</v>
+        <v>163.9069793070509</v>
       </c>
       <c r="E62">
-        <v>289.4160314602482</v>
+        <v>294.360630673742</v>
       </c>
       <c r="F62">
-        <v>296.6759528096276</v>
+        <v>301.6205520231214</v>
       </c>
       <c r="G62">
         <v>0.249</v>
@@ -7255,37 +7255,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M62">
-        <v>69.95618967251019</v>
+        <v>71.12212616705203</v>
       </c>
       <c r="N62">
-        <v>-60.82018967251019</v>
+        <v>-61.98612616705203</v>
       </c>
       <c r="O62">
-        <v>-13.38044172795224</v>
+        <v>-13.63694775675145</v>
       </c>
       <c r="P62">
-        <v>-47.43974794455795</v>
+        <v>-48.34917841030058</v>
       </c>
       <c r="Q62">
-        <v>-44.15974794455795</v>
+        <v>-45.06917841030058</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1817862246222126</v>
+        <v>0.1852730508945771</v>
       </c>
       <c r="T62">
-        <v>3.140559460097289</v>
+        <v>3.22108662574081</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.02873112457109443</v>
+        <v>0.02826012252894535</v>
       </c>
       <c r="W62">
-        <v>0.2290252008261359</v>
+        <v>0.2291362631076747</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.130596020777702</v>
+        <v>0.128455102404297</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2120296103445666</v>
+        <v>0.2139296103445666</v>
       </c>
       <c r="C63">
-        <v>-137.4645727160705</v>
+        <v>-144.2614527981463</v>
       </c>
       <c r="D63">
-        <v>163.9069793070509</v>
+        <v>162.0546984384688</v>
       </c>
       <c r="E63">
-        <v>294.360630673742</v>
+        <v>299.3052298872358</v>
       </c>
       <c r="F63">
-        <v>301.6205520231214</v>
+        <v>306.5651512366152</v>
       </c>
       <c r="G63">
         <v>0.249</v>
@@ -7337,37 +7337,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M63">
-        <v>71.12212616705203</v>
+        <v>72.28806266159386</v>
       </c>
       <c r="N63">
-        <v>-61.98612616705203</v>
+        <v>-63.15206266159385</v>
       </c>
       <c r="O63">
-        <v>-13.63694775675145</v>
+        <v>-13.89345378555065</v>
       </c>
       <c r="P63">
-        <v>-48.34917841030058</v>
+        <v>-49.2586088760432</v>
       </c>
       <c r="Q63">
-        <v>-45.06917841030058</v>
+        <v>-45.9786088760432</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1852730508945771</v>
+        <v>0.1889433943391712</v>
       </c>
       <c r="T63">
-        <v>3.22108662574081</v>
+        <v>3.305852063260305</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02826012252894535</v>
+        <v>0.02780431410105913</v>
       </c>
       <c r="W63">
-        <v>0.2291362631076747</v>
+        <v>0.2292437427349703</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.128455102404297</v>
+        <v>0.1263832459139052</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2139296103445666</v>
+        <v>0.2158296103445666</v>
       </c>
       <c r="C64">
-        <v>-144.2614527981463</v>
+        <v>-151.016936165342</v>
       </c>
       <c r="D64">
-        <v>162.0546984384688</v>
+        <v>160.243814284767</v>
       </c>
       <c r="E64">
-        <v>299.3052298872358</v>
+        <v>304.2498291007296</v>
       </c>
       <c r="F64">
-        <v>306.5651512366152</v>
+        <v>311.509750450109</v>
       </c>
       <c r="G64">
         <v>0.249</v>
@@ -7419,37 +7419,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M64">
-        <v>72.28806266159386</v>
+        <v>73.45399915613569</v>
       </c>
       <c r="N64">
-        <v>-63.15206266159385</v>
+        <v>-64.3179991561357</v>
       </c>
       <c r="O64">
-        <v>-13.89345378555065</v>
+        <v>-14.14995981434985</v>
       </c>
       <c r="P64">
-        <v>-49.2586088760432</v>
+        <v>-50.16803934178584</v>
       </c>
       <c r="Q64">
-        <v>-45.9786088760432</v>
+        <v>-46.88803934178584</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1889433943391712</v>
+        <v>0.1928121347267164</v>
       </c>
       <c r="T64">
-        <v>3.305852063260305</v>
+        <v>3.395199416321394</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02780431410105913</v>
+        <v>0.0273629757819947</v>
       </c>
       <c r="W64">
-        <v>0.2292437427349703</v>
+        <v>0.2293478103106057</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1263832459139052</v>
+        <v>0.1243771626454304</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2158296103445666</v>
+        <v>0.2177296103445666</v>
       </c>
       <c r="C65">
-        <v>-151.016936165342</v>
+        <v>-157.7323952471906</v>
       </c>
       <c r="D65">
-        <v>160.243814284767</v>
+        <v>158.4729544164122</v>
       </c>
       <c r="E65">
-        <v>304.2498291007296</v>
+        <v>309.1944283142234</v>
       </c>
       <c r="F65">
-        <v>311.509750450109</v>
+        <v>316.4543496636028</v>
       </c>
       <c r="G65">
         <v>0.249</v>
@@ -7501,37 +7501,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M65">
-        <v>73.45399915613569</v>
+        <v>74.61993565067753</v>
       </c>
       <c r="N65">
-        <v>-64.3179991561357</v>
+        <v>-65.48393565067754</v>
       </c>
       <c r="O65">
-        <v>-14.14995981434985</v>
+        <v>-14.40646584314906</v>
       </c>
       <c r="P65">
-        <v>-50.16803934178584</v>
+        <v>-51.07746980752848</v>
       </c>
       <c r="Q65">
-        <v>-46.88803934178584</v>
+        <v>-47.79746980752848</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1928121347267164</v>
+        <v>0.1968958051357918</v>
       </c>
       <c r="T65">
-        <v>3.395199416321394</v>
+        <v>3.489510511219211</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.0273629757819947</v>
+        <v>0.02693542928540103</v>
       </c>
       <c r="W65">
-        <v>0.2293478103106057</v>
+        <v>0.2294486257745025</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1243771626454304</v>
+        <v>0.1224337694790956</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2177296103445666</v>
+        <v>0.2196296103445666</v>
       </c>
       <c r="C66">
-        <v>-157.7323952471906</v>
+        <v>-164.4091424692679</v>
       </c>
       <c r="D66">
-        <v>158.4729544164122</v>
+        <v>156.7408064078287</v>
       </c>
       <c r="E66">
-        <v>309.1944283142234</v>
+        <v>314.1390275277172</v>
       </c>
       <c r="F66">
-        <v>316.4543496636028</v>
+        <v>321.3989488770966</v>
       </c>
       <c r="G66">
         <v>0.249</v>
@@ -7583,37 +7583,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M66">
-        <v>74.61993565067753</v>
+        <v>75.78587214521937</v>
       </c>
       <c r="N66">
-        <v>-65.48393565067754</v>
+        <v>-66.64987214521938</v>
       </c>
       <c r="O66">
-        <v>-14.40646584314906</v>
+        <v>-14.66297187194826</v>
       </c>
       <c r="P66">
-        <v>-51.07746980752848</v>
+        <v>-51.98690027327111</v>
       </c>
       <c r="Q66">
-        <v>-47.79746980752848</v>
+        <v>-48.70690027327111</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1968958051357918</v>
+        <v>0.2012128281396716</v>
       </c>
       <c r="T66">
-        <v>3.489510511219211</v>
+        <v>3.58921081153976</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02693542928540103</v>
+        <v>0.02652103806562563</v>
       </c>
       <c r="W66">
-        <v>0.2294486257745025</v>
+        <v>0.2295463392241255</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1224337694790956</v>
+        <v>0.120550173025571</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2196296103445666</v>
+        <v>0.2215296103445666</v>
       </c>
       <c r="C67">
-        <v>-164.4091424692679</v>
+        <v>-171.0484334970264</v>
       </c>
       <c r="D67">
-        <v>156.7408064078287</v>
+        <v>155.046114593564</v>
       </c>
       <c r="E67">
-        <v>314.1390275277172</v>
+        <v>319.083626741211</v>
       </c>
       <c r="F67">
-        <v>321.3989488770966</v>
+        <v>326.3435480905904</v>
       </c>
       <c r="G67">
         <v>0.249</v>
@@ -7665,37 +7665,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M67">
-        <v>75.78587214521937</v>
+        <v>76.95180863976121</v>
       </c>
       <c r="N67">
-        <v>-66.64987214521938</v>
+        <v>-67.81580863976122</v>
       </c>
       <c r="O67">
-        <v>-14.66297187194826</v>
+        <v>-14.91947790074747</v>
       </c>
       <c r="P67">
-        <v>-51.98690027327111</v>
+        <v>-52.89633073901375</v>
       </c>
       <c r="Q67">
-        <v>-48.70690027327111</v>
+        <v>-49.61633073901375</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2012128281396716</v>
+        <v>0.2057837936731914</v>
       </c>
       <c r="T67">
-        <v>3.58921081153976</v>
+        <v>3.694775835408577</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02652103806562563</v>
+        <v>0.02611920415554039</v>
       </c>
       <c r="W67">
-        <v>0.2295463392241255</v>
+        <v>0.2296410916601236</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.120550173025571</v>
+        <v>0.1187236552524563</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2215296103445666</v>
+        <v>0.2234296103445666</v>
       </c>
       <c r="C68">
-        <v>-171.0484334970264</v>
+        <v>-177.6514702714445</v>
       </c>
       <c r="D68">
-        <v>155.046114593564</v>
+        <v>153.3876770326397</v>
       </c>
       <c r="E68">
-        <v>319.083626741211</v>
+        <v>324.0282259547049</v>
       </c>
       <c r="F68">
-        <v>326.3435480905904</v>
+        <v>331.2881473040842</v>
       </c>
       <c r="G68">
         <v>0.249</v>
@@ -7747,37 +7747,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M68">
-        <v>76.95180863976121</v>
+        <v>78.11774513430305</v>
       </c>
       <c r="N68">
-        <v>-67.81580863976122</v>
+        <v>-68.98174513430305</v>
       </c>
       <c r="O68">
-        <v>-14.91947790074747</v>
+        <v>-15.17598392954667</v>
       </c>
       <c r="P68">
-        <v>-52.89633073901375</v>
+        <v>-53.80576120475638</v>
       </c>
       <c r="Q68">
-        <v>-49.61633073901375</v>
+        <v>-50.52576120475638</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2057837936731914</v>
+        <v>0.2106317874208638</v>
       </c>
       <c r="T68">
-        <v>3.694775835408577</v>
+        <v>3.806738739511867</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02611920415554039</v>
+        <v>0.02572936528754725</v>
       </c>
       <c r="W68">
-        <v>0.2296410916601236</v>
+        <v>0.2297330156651964</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1187236552524563</v>
+        <v>0.116951660397942</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2234296103445666</v>
+        <v>0.2253296103445666</v>
       </c>
       <c r="C69">
-        <v>-177.6514702714445</v>
+        <v>-184.2194038519135</v>
       </c>
       <c r="D69">
-        <v>153.3876770326397</v>
+        <v>151.7643426656645</v>
       </c>
       <c r="E69">
-        <v>324.0282259547049</v>
+        <v>328.9728251681987</v>
       </c>
       <c r="F69">
-        <v>331.2881473040842</v>
+        <v>336.232746517578</v>
       </c>
       <c r="G69">
         <v>0.249</v>
@@ -7829,37 +7829,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M69">
-        <v>78.11774513430305</v>
+        <v>79.28368162884489</v>
       </c>
       <c r="N69">
-        <v>-68.98174513430305</v>
+        <v>-70.14768162884489</v>
       </c>
       <c r="O69">
-        <v>-15.17598392954667</v>
+        <v>-15.43248995834588</v>
       </c>
       <c r="P69">
-        <v>-53.80576120475638</v>
+        <v>-54.71519167049902</v>
       </c>
       <c r="Q69">
-        <v>-50.52576120475638</v>
+        <v>-51.43519167049902</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2106317874208638</v>
+        <v>0.2157827807777658</v>
       </c>
       <c r="T69">
-        <v>3.806738739511867</v>
+        <v>3.925699325121613</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02572936528754725</v>
+        <v>0.02535099226861273</v>
       </c>
       <c r="W69">
-        <v>0.2297330156651964</v>
+        <v>0.2298222360230611</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.116951660397942</v>
+        <v>0.1152317830391487</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2253296103445666</v>
+        <v>0.2272296103445666</v>
       </c>
       <c r="C70">
-        <v>-184.2194038519135</v>
+        <v>-190.7533370804952</v>
       </c>
       <c r="D70">
-        <v>151.7643426656645</v>
+        <v>150.1750086505765</v>
       </c>
       <c r="E70">
-        <v>328.9728251681987</v>
+        <v>333.9174243816924</v>
       </c>
       <c r="F70">
-        <v>336.232746517578</v>
+        <v>341.1773457310717</v>
       </c>
       <c r="G70">
         <v>0.249</v>
@@ -7911,37 +7911,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M70">
-        <v>79.28368162884489</v>
+        <v>80.44961812338671</v>
       </c>
       <c r="N70">
-        <v>-70.14768162884489</v>
+        <v>-71.31361812338672</v>
       </c>
       <c r="O70">
-        <v>-15.43248995834588</v>
+        <v>-15.68899598714508</v>
       </c>
       <c r="P70">
-        <v>-54.71519167049902</v>
+        <v>-55.62462213624164</v>
       </c>
       <c r="Q70">
-        <v>-51.43519167049902</v>
+        <v>-52.34462213624164</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2157827807777658</v>
+        <v>0.2212660962867261</v>
       </c>
       <c r="T70">
-        <v>3.925699325121613</v>
+        <v>4.052334787222311</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02535099226861273</v>
+        <v>0.02498358658356038</v>
       </c>
       <c r="W70">
-        <v>0.2298222360230611</v>
+        <v>0.2299088702835965</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1152317830391487</v>
+        <v>0.1135617571980017</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2272296103445666</v>
+        <v>0.2291296103445666</v>
       </c>
       <c r="C71">
-        <v>-190.7533370804952</v>
+        <v>-197.2543270805063</v>
       </c>
       <c r="D71">
-        <v>150.1750086505765</v>
+        <v>148.6186178640592</v>
       </c>
       <c r="E71">
-        <v>333.9174243816924</v>
+        <v>338.8620235951862</v>
       </c>
       <c r="F71">
-        <v>341.1773457310717</v>
+        <v>346.1219449445655</v>
       </c>
       <c r="G71">
         <v>0.249</v>
@@ -7993,37 +7993,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M71">
-        <v>80.44961812338671</v>
+        <v>81.61555461792855</v>
       </c>
       <c r="N71">
-        <v>-71.31361812338672</v>
+        <v>-72.47955461792856</v>
       </c>
       <c r="O71">
-        <v>-15.68899598714508</v>
+        <v>-15.94550201594428</v>
       </c>
       <c r="P71">
-        <v>-55.62462213624164</v>
+        <v>-56.53405260198427</v>
       </c>
       <c r="Q71">
-        <v>-52.34462213624164</v>
+        <v>-53.25405260198427</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2212660962867261</v>
+        <v>0.2271149661629502</v>
       </c>
       <c r="T71">
-        <v>4.052334787222311</v>
+        <v>4.187412613463054</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02498358658356038</v>
+        <v>0.02462667820379523</v>
       </c>
       <c r="W71">
-        <v>0.2299088702835965</v>
+        <v>0.2299930292795451</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1135617571980017</v>
+        <v>0.1119394463808874</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2291296103445666</v>
+        <v>0.2310296103445666</v>
       </c>
       <c r="C72">
-        <v>-197.2543270805063</v>
+        <v>-203.723387601328</v>
       </c>
       <c r="D72">
-        <v>148.6186178640592</v>
+        <v>147.0941565567313</v>
       </c>
       <c r="E72">
-        <v>338.8620235951862</v>
+        <v>343.80662280868</v>
       </c>
       <c r="F72">
-        <v>346.1219449445655</v>
+        <v>351.0665441580593</v>
       </c>
       <c r="G72">
         <v>0.249</v>
@@ -8075,37 +8075,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M72">
-        <v>81.61555461792855</v>
+        <v>82.78149111247039</v>
       </c>
       <c r="N72">
-        <v>-72.47955461792856</v>
+        <v>-73.6454911124704</v>
       </c>
       <c r="O72">
-        <v>-15.94550201594428</v>
+        <v>-16.20200804474349</v>
       </c>
       <c r="P72">
-        <v>-56.53405260198427</v>
+        <v>-57.44348306772691</v>
       </c>
       <c r="Q72">
-        <v>-53.25405260198427</v>
+        <v>-54.16348306772691</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2271149661629502</v>
+        <v>0.2333672063754658</v>
       </c>
       <c r="T72">
-        <v>4.187412613463054</v>
+        <v>4.331806151858332</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02462667820379523</v>
+        <v>0.02427982358120656</v>
       </c>
       <c r="W72">
-        <v>0.2299930292795451</v>
+        <v>0.2300748175995515</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1119394463808874</v>
+        <v>0.1103628344600298</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2310296103445666</v>
+        <v>0.2329296103445666</v>
       </c>
       <c r="C73">
-        <v>-203.7233876013279</v>
+        <v>-210.1614912203681</v>
       </c>
       <c r="D73">
-        <v>147.0941565567313</v>
+        <v>145.600652151185</v>
       </c>
       <c r="E73">
-        <v>343.8066228086799</v>
+        <v>348.7512220221737</v>
       </c>
       <c r="F73">
-        <v>351.0665441580593</v>
+        <v>356.0111433715531</v>
       </c>
       <c r="G73">
         <v>0.249</v>
@@ -8157,37 +8157,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M73">
-        <v>82.78149111247038</v>
+        <v>83.94742760701222</v>
       </c>
       <c r="N73">
-        <v>-73.64549111247038</v>
+        <v>-74.81142760701222</v>
       </c>
       <c r="O73">
-        <v>-16.20200804474348</v>
+        <v>-16.45851407354269</v>
       </c>
       <c r="P73">
-        <v>-57.4434830677269</v>
+        <v>-58.35291353346953</v>
       </c>
       <c r="Q73">
-        <v>-54.1634830677269</v>
+        <v>-55.07291353346953</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2333672063754657</v>
+        <v>0.2400660351745895</v>
       </c>
       <c r="T73">
-        <v>4.331806151858331</v>
+        <v>4.486513514424699</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02427982358120657</v>
+        <v>0.02394260380924536</v>
       </c>
       <c r="W73">
-        <v>0.2300748175995515</v>
+        <v>0.23015433402178</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1103628344600298</v>
+        <v>0.1088300173147516</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2329296103445666</v>
+        <v>0.2348296103445666</v>
       </c>
       <c r="C74">
-        <v>-210.1614912203681</v>
+        <v>-216.5695714122282</v>
       </c>
       <c r="D74">
-        <v>145.600652151185</v>
+        <v>144.1371711728187</v>
       </c>
       <c r="E74">
-        <v>348.7512220221737</v>
+        <v>353.6958212356676</v>
       </c>
       <c r="F74">
-        <v>356.0111433715531</v>
+        <v>360.9557425850469</v>
       </c>
       <c r="G74">
         <v>0.249</v>
@@ -8239,37 +8239,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M74">
-        <v>83.94742760701222</v>
+        <v>85.11336410155405</v>
       </c>
       <c r="N74">
-        <v>-74.81142760701222</v>
+        <v>-75.97736410155406</v>
       </c>
       <c r="O74">
-        <v>-16.45851407354269</v>
+        <v>-16.71502010234189</v>
       </c>
       <c r="P74">
-        <v>-58.35291353346953</v>
+        <v>-59.26234399921216</v>
       </c>
       <c r="Q74">
-        <v>-55.07291353346953</v>
+        <v>-55.98234399921216</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2400660351745895</v>
+        <v>0.2472610735143891</v>
       </c>
       <c r="T74">
-        <v>4.486513514424699</v>
+        <v>4.652680681625614</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02394260380924536</v>
+        <v>0.02361462293514611</v>
       </c>
       <c r="W74">
-        <v>0.23015433402178</v>
+        <v>0.2302316719118925</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1088300173147516</v>
+        <v>0.107339195159755</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2348296103445666</v>
+        <v>0.2367296103445666</v>
       </c>
       <c r="C75">
-        <v>-216.5695714122282</v>
+        <v>-222.9485244943237</v>
       </c>
       <c r="D75">
-        <v>144.1371711728187</v>
+        <v>142.7028173042169</v>
       </c>
       <c r="E75">
-        <v>353.6958212356676</v>
+        <v>358.6404204491614</v>
       </c>
       <c r="F75">
-        <v>360.9557425850469</v>
+        <v>365.9003417985407</v>
       </c>
       <c r="G75">
         <v>0.249</v>
@@ -8321,37 +8321,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M75">
-        <v>85.11336410155405</v>
+        <v>86.27930059609589</v>
       </c>
       <c r="N75">
-        <v>-75.97736410155406</v>
+        <v>-77.1433005960959</v>
       </c>
       <c r="O75">
-        <v>-16.71502010234189</v>
+        <v>-16.9715261311411</v>
       </c>
       <c r="P75">
-        <v>-59.26234399921216</v>
+        <v>-60.1717744649548</v>
       </c>
       <c r="Q75">
-        <v>-55.98234399921216</v>
+        <v>-56.8917744649548</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2472610735143891</v>
+        <v>0.2550095763418656</v>
       </c>
       <c r="T75">
-        <v>4.652680681625614</v>
+        <v>4.831629938611214</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02361462293514611</v>
+        <v>0.02329550640899549</v>
       </c>
       <c r="W75">
-        <v>0.2302316719118925</v>
+        <v>0.2303069195887589</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.107339195159755</v>
+        <v>0.105888665495434</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2367296103445666</v>
+        <v>0.2386296103445666</v>
       </c>
       <c r="C76">
-        <v>-222.9485244943237</v>
+        <v>-229.2992114574817</v>
       </c>
       <c r="D76">
-        <v>142.7028173042169</v>
+        <v>141.2967295545528</v>
       </c>
       <c r="E76">
-        <v>358.6404204491614</v>
+        <v>363.5850196626552</v>
       </c>
       <c r="F76">
-        <v>365.9003417985407</v>
+        <v>370.8449410120345</v>
       </c>
       <c r="G76">
         <v>0.249</v>
@@ -8403,37 +8403,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M76">
-        <v>86.27930059609589</v>
+        <v>87.44523709063773</v>
       </c>
       <c r="N76">
-        <v>-77.1433005960959</v>
+        <v>-78.30923709063774</v>
       </c>
       <c r="O76">
-        <v>-16.9715261311411</v>
+        <v>-17.2280321599403</v>
       </c>
       <c r="P76">
-        <v>-60.1717744649548</v>
+        <v>-61.08120493069744</v>
       </c>
       <c r="Q76">
-        <v>-56.8917744649548</v>
+        <v>-57.80120493069744</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2550095763418656</v>
+        <v>0.2633779593955402</v>
       </c>
       <c r="T76">
-        <v>4.831629938611214</v>
+        <v>5.024895136155664</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02329550640899549</v>
+        <v>0.02298489965687555</v>
       </c>
       <c r="W76">
-        <v>0.2303069195887589</v>
+        <v>0.2303801606609087</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.105888665495434</v>
+        <v>0.1044768166221616</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2386296103445666</v>
+        <v>0.2405296103445666</v>
       </c>
       <c r="C77">
-        <v>-229.2992114574817</v>
+        <v>-235.6224596893689</v>
       </c>
       <c r="D77">
-        <v>141.2967295545528</v>
+        <v>139.9180805361594</v>
       </c>
       <c r="E77">
-        <v>363.5850196626552</v>
+        <v>368.529618876149</v>
       </c>
       <c r="F77">
-        <v>370.8449410120345</v>
+        <v>375.7895402255283</v>
       </c>
       <c r="G77">
         <v>0.249</v>
@@ -8485,37 +8485,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M77">
-        <v>87.44523709063773</v>
+        <v>88.61117358517957</v>
       </c>
       <c r="N77">
-        <v>-78.30923709063774</v>
+        <v>-79.47517358517958</v>
       </c>
       <c r="O77">
-        <v>-17.2280321599403</v>
+        <v>-17.48453818873951</v>
       </c>
       <c r="P77">
-        <v>-61.08120493069744</v>
+        <v>-61.99063539644007</v>
       </c>
       <c r="Q77">
-        <v>-57.80120493069744</v>
+        <v>-58.71063539644007</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2633779593955402</v>
+        <v>0.2724437077036878</v>
       </c>
       <c r="T77">
-        <v>5.024895136155664</v>
+        <v>5.234265766828817</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02298489965687555</v>
+        <v>0.0226824667666535</v>
       </c>
       <c r="W77">
-        <v>0.2303801606609087</v>
+        <v>0.2304514743364231</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1044768166221616</v>
+        <v>0.1031021216666068</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2405296103445666</v>
+        <v>0.2424296103445666</v>
       </c>
       <c r="C78">
-        <v>-235.6224596893689</v>
+        <v>-241.9190645980011</v>
       </c>
       <c r="D78">
-        <v>139.9180805361594</v>
+        <v>138.566074841021</v>
       </c>
       <c r="E78">
-        <v>368.529618876149</v>
+        <v>373.4742180896428</v>
       </c>
       <c r="F78">
-        <v>375.7895402255283</v>
+        <v>380.7341394390221</v>
       </c>
       <c r="G78">
         <v>0.249</v>
@@ -8567,37 +8567,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M78">
-        <v>88.61117358517957</v>
+        <v>89.77711007972141</v>
       </c>
       <c r="N78">
-        <v>-79.47517358517958</v>
+        <v>-80.64111007972141</v>
       </c>
       <c r="O78">
-        <v>-17.48453818873951</v>
+        <v>-17.74104421753871</v>
       </c>
       <c r="P78">
-        <v>-61.99063539644007</v>
+        <v>-62.9000658621827</v>
       </c>
       <c r="Q78">
-        <v>-58.71063539644007</v>
+        <v>-59.6200658621827</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2724437077036878</v>
+        <v>0.2822977819516741</v>
       </c>
       <c r="T78">
-        <v>5.234265766828817</v>
+        <v>5.461842539299633</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.0226824667666535</v>
+        <v>0.02238788927617748</v>
       </c>
       <c r="W78">
-        <v>0.2304514743364231</v>
+        <v>0.2305209357086773</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1031021216666068</v>
+        <v>0.1017631330735339</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2424296103445666</v>
+        <v>0.2443296103445666</v>
       </c>
       <c r="C79">
-        <v>-241.9190645980011</v>
+        <v>-248.1897911420276</v>
       </c>
       <c r="D79">
-        <v>138.566074841021</v>
+        <v>137.2399475104883</v>
       </c>
       <c r="E79">
-        <v>373.4742180896428</v>
+        <v>378.4188173031366</v>
       </c>
       <c r="F79">
-        <v>380.7341394390221</v>
+        <v>385.6787386525159</v>
       </c>
       <c r="G79">
         <v>0.249</v>
@@ -8649,37 +8649,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M79">
-        <v>89.77711007972141</v>
+        <v>90.94304657426325</v>
       </c>
       <c r="N79">
-        <v>-80.64111007972141</v>
+        <v>-81.80704657426325</v>
       </c>
       <c r="O79">
-        <v>-17.74104421753871</v>
+        <v>-17.99755024633792</v>
       </c>
       <c r="P79">
-        <v>-62.9000658621827</v>
+        <v>-63.80949632792534</v>
       </c>
       <c r="Q79">
-        <v>-59.6200658621827</v>
+        <v>-60.52949632792534</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2822977819516741</v>
+        <v>0.2930476811312957</v>
       </c>
       <c r="T79">
-        <v>5.461842539299633</v>
+        <v>5.7101081092678</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02238788927617748</v>
+        <v>0.02210086505468803</v>
       </c>
       <c r="W79">
-        <v>0.2305209357086773</v>
+        <v>0.2305886160201046</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1017631330735339</v>
+        <v>0.1004584775213091</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2443296103445666</v>
+        <v>0.2462296103445666</v>
       </c>
       <c r="C80">
-        <v>-248.1897911420276</v>
+        <v>-254.4353752739756</v>
       </c>
       <c r="D80">
-        <v>137.2399475104883</v>
+        <v>135.9389625920341</v>
       </c>
       <c r="E80">
-        <v>378.4188173031366</v>
+        <v>383.3634165166304</v>
       </c>
       <c r="F80">
-        <v>385.6787386525159</v>
+        <v>390.6233378660097</v>
       </c>
       <c r="G80">
         <v>0.249</v>
@@ -8731,37 +8731,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M80">
-        <v>90.94304657426325</v>
+        <v>92.10898306880509</v>
       </c>
       <c r="N80">
-        <v>-81.80704657426325</v>
+        <v>-82.97298306880509</v>
       </c>
       <c r="O80">
-        <v>-17.99755024633792</v>
+        <v>-18.25405627513712</v>
       </c>
       <c r="P80">
-        <v>-63.80949632792534</v>
+        <v>-64.71892679366798</v>
       </c>
       <c r="Q80">
-        <v>-60.52949632792534</v>
+        <v>-61.43892679366797</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2930476811312957</v>
+        <v>0.304821380232786</v>
       </c>
       <c r="T80">
-        <v>5.7101081092678</v>
+        <v>5.982018019232934</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02210086505468803</v>
+        <v>0.02182110726918565</v>
       </c>
       <c r="W80">
-        <v>0.2305886160201046</v>
+        <v>0.230654582905926</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1004584775213091</v>
+        <v>0.09918685122357107</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2462296103445666</v>
+        <v>0.2481296103445667</v>
       </c>
       <c r="C81">
-        <v>-254.4353752739756</v>
+        <v>-260.6565253021772</v>
       </c>
       <c r="D81">
-        <v>135.9389625920341</v>
+        <v>134.6624117773264</v>
       </c>
       <c r="E81">
-        <v>383.3634165166304</v>
+        <v>388.3080157301242</v>
       </c>
       <c r="F81">
-        <v>390.6233378660097</v>
+        <v>395.5679370795035</v>
       </c>
       <c r="G81">
         <v>0.249</v>
@@ -8813,37 +8813,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M81">
-        <v>92.10898306880509</v>
+        <v>93.27491956334693</v>
       </c>
       <c r="N81">
-        <v>-82.97298306880509</v>
+        <v>-84.13891956334693</v>
       </c>
       <c r="O81">
-        <v>-18.25405627513712</v>
+        <v>-18.51056230393633</v>
       </c>
       <c r="P81">
-        <v>-64.71892679366798</v>
+        <v>-65.62835725941061</v>
       </c>
       <c r="Q81">
-        <v>-61.43892679366797</v>
+        <v>-62.34835725941061</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.304821380232786</v>
+        <v>0.3177724492444253</v>
       </c>
       <c r="T81">
-        <v>5.982018019232934</v>
+        <v>6.28111892019458</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02182110726918565</v>
+        <v>0.02154834342832082</v>
       </c>
       <c r="W81">
-        <v>0.230654582905926</v>
+        <v>0.230718900619602</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.09918685122357107</v>
+        <v>0.09794701558327645</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2481296103445667</v>
+        <v>0.2500296103445667</v>
       </c>
       <c r="C82">
-        <v>-260.6565253021772</v>
+        <v>-266.8539231766744</v>
       </c>
       <c r="D82">
-        <v>134.6624117773264</v>
+        <v>133.4096131163229</v>
       </c>
       <c r="E82">
-        <v>388.3080157301242</v>
+        <v>393.252614943618</v>
       </c>
       <c r="F82">
-        <v>395.5679370795035</v>
+        <v>400.5125362929973</v>
       </c>
       <c r="G82">
         <v>0.249</v>
@@ -8895,37 +8895,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M82">
-        <v>93.27491956334693</v>
+        <v>94.44085605788877</v>
       </c>
       <c r="N82">
-        <v>-84.13891956334693</v>
+        <v>-85.30485605788877</v>
       </c>
       <c r="O82">
-        <v>-18.51056230393633</v>
+        <v>-18.76706833273553</v>
       </c>
       <c r="P82">
-        <v>-65.62835725941061</v>
+        <v>-66.53778772515324</v>
       </c>
       <c r="Q82">
-        <v>-62.34835725941061</v>
+        <v>-63.25778772515324</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3177724492444253</v>
+        <v>0.3320867886783425</v>
       </c>
       <c r="T82">
-        <v>6.28111892019458</v>
+        <v>6.611704126520612</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02154834342832082</v>
+        <v>0.02128231449710699</v>
       </c>
       <c r="W82">
-        <v>0.230718900619602</v>
+        <v>0.2307816302415822</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.09794701558327645</v>
+        <v>0.09673779316866804</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2500296103445667</v>
+        <v>0.2519296103445666</v>
       </c>
       <c r="C83">
-        <v>-266.8539231766744</v>
+        <v>-273.0282257040069</v>
       </c>
       <c r="D83">
-        <v>133.4096131163229</v>
+        <v>132.1799098024841</v>
       </c>
       <c r="E83">
-        <v>393.252614943618</v>
+        <v>398.1972141571117</v>
       </c>
       <c r="F83">
-        <v>400.5125362929973</v>
+        <v>405.4571355064911</v>
       </c>
       <c r="G83">
         <v>0.249</v>
@@ -8977,37 +8977,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M83">
-        <v>94.44085605788877</v>
+        <v>95.60679255243059</v>
       </c>
       <c r="N83">
-        <v>-85.30485605788877</v>
+        <v>-86.47079255243059</v>
       </c>
       <c r="O83">
-        <v>-18.76706833273553</v>
+        <v>-19.02357436153473</v>
       </c>
       <c r="P83">
-        <v>-66.53778772515324</v>
+        <v>-67.44721819089587</v>
       </c>
       <c r="Q83">
-        <v>-63.25778772515324</v>
+        <v>-64.16721819089587</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3320867886783425</v>
+        <v>0.3479916102715837</v>
       </c>
       <c r="T83">
-        <v>6.611704126520612</v>
+        <v>6.979021022438423</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02128231449710699</v>
+        <v>0.02102277407641056</v>
       </c>
       <c r="W83">
-        <v>0.2307816302415822</v>
+        <v>0.2308428298727824</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.09673779316866804</v>
+        <v>0.09555806398368427</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2519296103445666</v>
+        <v>0.2538296103445666</v>
       </c>
       <c r="C84">
-        <v>-273.0282257040069</v>
+        <v>-279.1800656954301</v>
       </c>
       <c r="D84">
-        <v>132.1799098024841</v>
+        <v>130.9726690245548</v>
       </c>
       <c r="E84">
-        <v>398.1972141571117</v>
+        <v>403.1418133706055</v>
       </c>
       <c r="F84">
-        <v>405.4571355064911</v>
+        <v>410.4017347199849</v>
       </c>
       <c r="G84">
         <v>0.249</v>
@@ -9059,37 +9059,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M84">
-        <v>95.60679255243059</v>
+        <v>96.77272904697243</v>
       </c>
       <c r="N84">
-        <v>-86.47079255243059</v>
+        <v>-87.63672904697243</v>
       </c>
       <c r="O84">
-        <v>-19.02357436153473</v>
+        <v>-19.28008039033394</v>
       </c>
       <c r="P84">
-        <v>-67.44721819089587</v>
+        <v>-68.3566486566385</v>
       </c>
       <c r="Q84">
-        <v>-64.16721819089587</v>
+        <v>-65.0766486566385</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3479916102715837</v>
+        <v>0.3657675873463828</v>
       </c>
       <c r="T84">
-        <v>6.979021022438423</v>
+        <v>7.389551670817155</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02102277407641056</v>
+        <v>0.02076948764175501</v>
       </c>
       <c r="W84">
-        <v>0.2308428298727824</v>
+        <v>0.2309025548140742</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.09555806398368427</v>
+        <v>0.09440676200797726</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2538296103445666</v>
+        <v>0.2557296103445666</v>
       </c>
       <c r="C85">
-        <v>-279.1800656954301</v>
+        <v>-285.3100530527794</v>
       </c>
       <c r="D85">
-        <v>130.9726690245548</v>
+        <v>129.7872808806993</v>
       </c>
       <c r="E85">
-        <v>403.1418133706055</v>
+        <v>408.0864125840993</v>
       </c>
       <c r="F85">
-        <v>410.4017347199849</v>
+        <v>415.3463339334787</v>
       </c>
       <c r="G85">
         <v>0.249</v>
@@ -9141,37 +9141,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M85">
-        <v>96.77272904697243</v>
+        <v>97.93866554151427</v>
       </c>
       <c r="N85">
-        <v>-87.63672904697243</v>
+        <v>-88.80266554151427</v>
       </c>
       <c r="O85">
-        <v>-19.28008039033394</v>
+        <v>-19.53658641913314</v>
       </c>
       <c r="P85">
-        <v>-68.3566486566385</v>
+        <v>-69.26607912238113</v>
       </c>
       <c r="Q85">
-        <v>-65.0766486566385</v>
+        <v>-65.98607912238113</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3657675873463828</v>
+        <v>0.3857655615555318</v>
       </c>
       <c r="T85">
-        <v>7.389551670817155</v>
+        <v>7.851398650243228</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02076948764175501</v>
+        <v>0.02052223183649602</v>
       </c>
       <c r="W85">
-        <v>0.2309025548140742</v>
+        <v>0.2309608577329542</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.09440676200797726</v>
+        <v>0.09328287198407281</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2557296103445666</v>
+        <v>0.2576296103445666</v>
       </c>
       <c r="C86">
-        <v>-285.3100530527793</v>
+        <v>-291.4187757958978</v>
       </c>
       <c r="D86">
-        <v>129.7872808806993</v>
+        <v>128.6231573510747</v>
       </c>
       <c r="E86">
-        <v>408.0864125840993</v>
+        <v>413.0310117975931</v>
       </c>
       <c r="F86">
-        <v>415.3463339334786</v>
+        <v>420.2909331469724</v>
       </c>
       <c r="G86">
         <v>0.249</v>
@@ -9223,37 +9223,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M86">
-        <v>97.93866554151425</v>
+        <v>99.10460203605609</v>
       </c>
       <c r="N86">
-        <v>-88.80266554151426</v>
+        <v>-89.9686020360561</v>
       </c>
       <c r="O86">
-        <v>-19.53658641913314</v>
+        <v>-19.79309244793234</v>
       </c>
       <c r="P86">
-        <v>-69.26607912238111</v>
+        <v>-70.17550958812376</v>
       </c>
       <c r="Q86">
-        <v>-65.98607912238111</v>
+        <v>-66.89550958812376</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3857655615555315</v>
+        <v>0.4084299323259004</v>
       </c>
       <c r="T86">
-        <v>7.851398650243222</v>
+        <v>8.374825226926106</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02052223183649603</v>
+        <v>0.02028079381489019</v>
       </c>
       <c r="W86">
-        <v>0.2309608577329542</v>
+        <v>0.2310177888184489</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.09328287198407281</v>
+        <v>0.092185426431319</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2576296103445666</v>
+        <v>0.2595296103445667</v>
       </c>
       <c r="C87">
-        <v>-291.4187757958978</v>
+        <v>-297.5068010352617</v>
       </c>
       <c r="D87">
-        <v>128.6231573510747</v>
+        <v>127.4797313252046</v>
       </c>
       <c r="E87">
-        <v>413.0310117975931</v>
+        <v>417.9756110110869</v>
       </c>
       <c r="F87">
-        <v>420.2909331469724</v>
+        <v>425.2355323604662</v>
       </c>
       <c r="G87">
         <v>0.249</v>
@@ -9305,37 +9305,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M87">
-        <v>99.10460203605609</v>
+        <v>100.2705385305979</v>
       </c>
       <c r="N87">
-        <v>-89.9686020360561</v>
+        <v>-91.13453853059794</v>
       </c>
       <c r="O87">
-        <v>-19.79309244793234</v>
+        <v>-20.04959847673155</v>
       </c>
       <c r="P87">
-        <v>-70.17550958812376</v>
+        <v>-71.08494005386639</v>
       </c>
       <c r="Q87">
-        <v>-66.89550958812376</v>
+        <v>-67.80494005386639</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4084299323259004</v>
+        <v>0.434332070349179</v>
       </c>
       <c r="T87">
-        <v>8.374825226926106</v>
+        <v>8.973027028849399</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02028079381489019</v>
+        <v>0.02004497063099612</v>
       </c>
       <c r="W87">
-        <v>0.2310177888184489</v>
+        <v>0.2310733959252111</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.092185426431319</v>
+        <v>0.09111350286816411</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2595296103445667</v>
+        <v>0.2614296103445666</v>
       </c>
       <c r="C88">
-        <v>-297.5068010352617</v>
+        <v>-303.5746758931849</v>
       </c>
       <c r="D88">
-        <v>127.4797313252046</v>
+        <v>126.3564556807751</v>
       </c>
       <c r="E88">
-        <v>417.9756110110869</v>
+        <v>422.9202102245807</v>
       </c>
       <c r="F88">
-        <v>425.2355323604662</v>
+        <v>430.18013157396</v>
       </c>
       <c r="G88">
         <v>0.249</v>
@@ -9387,37 +9387,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M88">
-        <v>100.2705385305979</v>
+        <v>101.4364750251398</v>
       </c>
       <c r="N88">
-        <v>-91.13453853059794</v>
+        <v>-92.30047502513978</v>
       </c>
       <c r="O88">
-        <v>-20.04959847673155</v>
+        <v>-20.30610450553075</v>
       </c>
       <c r="P88">
-        <v>-71.08494005386639</v>
+        <v>-71.99437051960902</v>
       </c>
       <c r="Q88">
-        <v>-67.80494005386639</v>
+        <v>-68.71437051960902</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.434332070349179</v>
+        <v>0.4642191526837312</v>
       </c>
       <c r="T88">
-        <v>8.973027028849399</v>
+        <v>9.663259877222428</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02004497063099612</v>
+        <v>0.0198145686697203</v>
       </c>
       <c r="W88">
-        <v>0.2310733959252111</v>
+        <v>0.2311277247076799</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.09111350286816411</v>
+        <v>0.09006622122600128</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2614296103445666</v>
+        <v>0.2633296103445666</v>
       </c>
       <c r="C89">
-        <v>-303.5746758931849</v>
+        <v>-309.6229283767472</v>
       </c>
       <c r="D89">
-        <v>126.3564556807751</v>
+        <v>125.2528024107067</v>
       </c>
       <c r="E89">
-        <v>422.9202102245807</v>
+        <v>427.8648094380745</v>
       </c>
       <c r="F89">
-        <v>430.18013157396</v>
+        <v>435.1247307874538</v>
       </c>
       <c r="G89">
         <v>0.249</v>
@@ -9469,37 +9469,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M89">
-        <v>101.4364750251398</v>
+        <v>102.6024115196816</v>
       </c>
       <c r="N89">
-        <v>-92.30047502513978</v>
+        <v>-93.46641151968161</v>
       </c>
       <c r="O89">
-        <v>-20.30610450553075</v>
+        <v>-20.56261053432996</v>
       </c>
       <c r="P89">
-        <v>-71.99437051960902</v>
+        <v>-72.90380098535167</v>
       </c>
       <c r="Q89">
-        <v>-68.71437051960902</v>
+        <v>-69.62380098535166</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4642191526837312</v>
+        <v>0.4990874154073756</v>
       </c>
       <c r="T89">
-        <v>9.663259877222428</v>
+        <v>10.46853153365763</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0198145686697203</v>
+        <v>0.01958940311665529</v>
       </c>
       <c r="W89">
-        <v>0.2311277247076799</v>
+        <v>0.2311808187450927</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.09006622122600128</v>
+        <v>0.08904274143934221</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9515,22 +9515,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2633296103445666</v>
+        <v>0.2652296103445666</v>
       </c>
       <c r="C90">
-        <v>-309.6229283767472</v>
+        <v>-315.6520682053687</v>
       </c>
       <c r="D90">
-        <v>125.2528024107067</v>
+        <v>124.1682617955789</v>
       </c>
       <c r="E90">
-        <v>427.8648094380745</v>
+        <v>432.8094086515683</v>
       </c>
       <c r="F90">
-        <v>435.1247307874538</v>
+        <v>440.0693300009476</v>
       </c>
       <c r="G90">
         <v>0.249</v>
@@ -9551,37 +9551,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M90">
-        <v>102.6024115196816</v>
+        <v>103.7683480142234</v>
       </c>
       <c r="N90">
-        <v>-93.46641151968161</v>
+        <v>-94.63234801422345</v>
       </c>
       <c r="O90">
-        <v>-20.56261053432996</v>
+        <v>-20.81911656312916</v>
       </c>
       <c r="P90">
-        <v>-72.90380098535167</v>
+        <v>-73.8132314510943</v>
       </c>
       <c r="Q90">
-        <v>-69.62380098535166</v>
+        <v>-70.5332314510943</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4990874154073756</v>
+        <v>0.5402953622625914</v>
       </c>
       <c r="T90">
-        <v>10.46853153365763</v>
+        <v>11.4202162185356</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01958940311665529</v>
+        <v>0.01936929746365917</v>
       </c>
       <c r="W90">
-        <v>0.2311808187450927</v>
+        <v>0.2312327196580692</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.08904274143934221</v>
+        <v>0.08804226119845071</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9597,22 +9597,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2652296103445666</v>
+        <v>0.2671296103445666</v>
       </c>
       <c r="C91">
-        <v>-315.6520682053687</v>
+        <v>-321.6625875957621</v>
       </c>
       <c r="D91">
-        <v>124.1682617955789</v>
+        <v>123.1023416186793</v>
       </c>
       <c r="E91">
-        <v>432.8094086515683</v>
+        <v>437.7540078650621</v>
       </c>
       <c r="F91">
-        <v>440.0693300009476</v>
+        <v>445.0139292144414</v>
       </c>
       <c r="G91">
         <v>0.249</v>
@@ -9633,37 +9633,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M91">
-        <v>103.7683480142234</v>
+        <v>104.9342845087653</v>
       </c>
       <c r="N91">
-        <v>-94.63234801422345</v>
+        <v>-95.79828450876529</v>
       </c>
       <c r="O91">
-        <v>-20.81911656312916</v>
+        <v>-21.07562259192837</v>
       </c>
       <c r="P91">
-        <v>-73.8132314510943</v>
+        <v>-74.72266191683693</v>
       </c>
       <c r="Q91">
-        <v>-70.5332314510943</v>
+        <v>-71.44266191683693</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5402953622625914</v>
+        <v>0.5897448984888506</v>
       </c>
       <c r="T91">
-        <v>11.4202162185356</v>
+        <v>12.56223784038916</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01936929746365917</v>
+        <v>0.01915408304739629</v>
       </c>
       <c r="W91">
-        <v>0.2312327196580692</v>
+        <v>0.231283467217424</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.08804226119845071</v>
+        <v>0.08706401385180129</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9679,22 +9679,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2671296103445666</v>
+        <v>0.2690296103445666</v>
       </c>
       <c r="C92">
-        <v>-321.6625875957621</v>
+        <v>-327.6549620067956</v>
       </c>
       <c r="D92">
-        <v>123.1023416186793</v>
+        <v>122.0545664211396</v>
       </c>
       <c r="E92">
-        <v>437.7540078650621</v>
+        <v>442.6986070785559</v>
       </c>
       <c r="F92">
-        <v>445.0139292144414</v>
+        <v>449.9585284279352</v>
       </c>
       <c r="G92">
         <v>0.249</v>
@@ -9715,37 +9715,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M92">
-        <v>104.9342845087653</v>
+        <v>106.1002210033071</v>
       </c>
       <c r="N92">
-        <v>-95.79828450876529</v>
+        <v>-96.96422100330713</v>
       </c>
       <c r="O92">
-        <v>-21.07562259192837</v>
+        <v>-21.33212862072757</v>
       </c>
       <c r="P92">
-        <v>-74.72266191683693</v>
+        <v>-75.63209238257956</v>
       </c>
       <c r="Q92">
-        <v>-71.44266191683693</v>
+        <v>-72.35209238257956</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5897448984888506</v>
+        <v>0.6501832205431674</v>
       </c>
       <c r="T92">
-        <v>12.56223784038916</v>
+        <v>13.95804204487685</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01915408304739629</v>
+        <v>0.01894359861830402</v>
       </c>
       <c r="W92">
-        <v>0.231283467217424</v>
+        <v>0.2313330994458039</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.08706401385180129</v>
+        <v>0.08610726644683642</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9761,22 +9761,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2690296103445666</v>
+        <v>0.2709296103445666</v>
       </c>
       <c r="C93">
-        <v>-327.6549620067956</v>
+        <v>-333.6296508466394</v>
       </c>
       <c r="D93">
-        <v>122.0545664211396</v>
+        <v>121.0244767947896</v>
       </c>
       <c r="E93">
-        <v>442.6986070785559</v>
+        <v>447.6432062920497</v>
       </c>
       <c r="F93">
-        <v>449.9585284279352</v>
+        <v>454.903127641429</v>
       </c>
       <c r="G93">
         <v>0.249</v>
@@ -9797,37 +9797,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M93">
-        <v>106.1002210033071</v>
+        <v>107.266157497849</v>
       </c>
       <c r="N93">
-        <v>-96.96422100330713</v>
+        <v>-98.13015749784897</v>
       </c>
       <c r="O93">
-        <v>-21.33212862072757</v>
+        <v>-21.58863464952677</v>
       </c>
       <c r="P93">
-        <v>-75.63209238257956</v>
+        <v>-76.54152284832219</v>
       </c>
       <c r="Q93">
-        <v>-72.35209238257956</v>
+        <v>-73.26152284832219</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6501832205431674</v>
+        <v>0.7257311231110635</v>
       </c>
       <c r="T93">
-        <v>13.95804204487685</v>
+        <v>15.70279730048646</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01894359861830402</v>
+        <v>0.01873768993767028</v>
       </c>
       <c r="W93">
-        <v>0.2313330994458039</v>
+        <v>0.2313816527126973</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.08610726644683642</v>
+        <v>0.08517131789850119</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9843,22 +9843,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2709296103445666</v>
+        <v>0.2728296103445666</v>
       </c>
       <c r="C94">
-        <v>-333.6296508466394</v>
+        <v>-339.5870981444034</v>
       </c>
       <c r="D94">
-        <v>121.0244767947896</v>
+        <v>120.0116287105194</v>
       </c>
       <c r="E94">
-        <v>447.6432062920497</v>
+        <v>452.5878055055435</v>
       </c>
       <c r="F94">
-        <v>454.903127641429</v>
+        <v>459.8477268549228</v>
       </c>
       <c r="G94">
         <v>0.249</v>
@@ -9879,37 +9879,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M94">
-        <v>107.266157497849</v>
+        <v>108.4320939923908</v>
       </c>
       <c r="N94">
-        <v>-98.13015749784897</v>
+        <v>-99.29609399239081</v>
       </c>
       <c r="O94">
-        <v>-21.58863464952677</v>
+        <v>-21.84514067832598</v>
       </c>
       <c r="P94">
-        <v>-76.54152284832219</v>
+        <v>-77.45095331406483</v>
       </c>
       <c r="Q94">
-        <v>-73.26152284832219</v>
+        <v>-74.17095331406483</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7257311231110635</v>
+        <v>0.8228641406983583</v>
       </c>
       <c r="T94">
-        <v>15.70279730048646</v>
+        <v>17.94605405769881</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01873768993767028</v>
+        <v>0.01853620940070608</v>
       </c>
       <c r="W94">
-        <v>0.2313816527126973</v>
+        <v>0.2314291618233135</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.08517131789850119</v>
+        <v>0.08425549727593673</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9925,22 +9925,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2728296103445666</v>
+        <v>0.2747296103445666</v>
       </c>
       <c r="C95">
-        <v>-339.5870981444034</v>
+        <v>-345.527733188329</v>
       </c>
       <c r="D95">
-        <v>120.0116287105194</v>
+        <v>119.0155928800876</v>
       </c>
       <c r="E95">
-        <v>452.5878055055435</v>
+        <v>457.5324047190372</v>
       </c>
       <c r="F95">
-        <v>459.8477268549228</v>
+        <v>464.7923260684166</v>
       </c>
       <c r="G95">
         <v>0.249</v>
@@ -9961,37 +9961,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M95">
-        <v>108.4320939923908</v>
+        <v>109.5980304869326</v>
       </c>
       <c r="N95">
-        <v>-99.29609399239081</v>
+        <v>-100.4620304869326</v>
       </c>
       <c r="O95">
-        <v>-21.84514067832598</v>
+        <v>-22.10164670712518</v>
       </c>
       <c r="P95">
-        <v>-77.45095331406483</v>
+        <v>-78.36038377980745</v>
       </c>
       <c r="Q95">
-        <v>-74.17095331406483</v>
+        <v>-75.08038377980745</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8228641406983583</v>
+        <v>0.9523748308147516</v>
       </c>
       <c r="T95">
-        <v>17.94605405769881</v>
+        <v>20.93706306731528</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01853620940070608</v>
+        <v>0.0183390156836773</v>
       </c>
       <c r="W95">
-        <v>0.2314291618233135</v>
+        <v>0.2314756601017889</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.08425549727593673</v>
+        <v>0.08335916219853312</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -10007,22 +10007,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2747296103445666</v>
+        <v>0.2766296103445667</v>
       </c>
       <c r="C96">
-        <v>-345.527733188329</v>
+        <v>-351.4519711324632</v>
       </c>
       <c r="D96">
-        <v>119.0155928800876</v>
+        <v>118.0359541494472</v>
       </c>
       <c r="E96">
-        <v>457.5324047190372</v>
+        <v>462.477003932531</v>
       </c>
       <c r="F96">
-        <v>464.7923260684166</v>
+        <v>469.7369252819104</v>
       </c>
       <c r="G96">
         <v>0.249</v>
@@ -10043,37 +10043,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M96">
-        <v>109.5980304869326</v>
+        <v>110.7639669814745</v>
       </c>
       <c r="N96">
-        <v>-100.4620304869326</v>
+        <v>-101.6279669814745</v>
       </c>
       <c r="O96">
-        <v>-22.10164670712518</v>
+        <v>-22.35815273592439</v>
       </c>
       <c r="P96">
-        <v>-78.36038377980745</v>
+        <v>-79.26981424555009</v>
       </c>
       <c r="Q96">
-        <v>-75.08038377980745</v>
+        <v>-75.98981424555009</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9523748308147516</v>
+        <v>1.133689796977703</v>
       </c>
       <c r="T96">
-        <v>20.93706306731528</v>
+        <v>25.12447568077835</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0183390156836773</v>
+        <v>0.0181459734133228</v>
       </c>
       <c r="W96">
-        <v>0.2314756601017889</v>
+        <v>0.2315211794691385</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.08335916219853312</v>
+        <v>0.08248169733328536</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -10089,22 +10089,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2766296103445667</v>
+        <v>0.2785296103445666</v>
       </c>
       <c r="C97">
-        <v>-351.4519711324632</v>
+        <v>-357.3602135736147</v>
       </c>
       <c r="D97">
-        <v>118.0359541494472</v>
+        <v>117.0723109217895</v>
       </c>
       <c r="E97">
-        <v>462.477003932531</v>
+        <v>467.4216031460248</v>
       </c>
       <c r="F97">
-        <v>469.7369252819104</v>
+        <v>474.6815244954042</v>
       </c>
       <c r="G97">
         <v>0.249</v>
@@ -10125,37 +10125,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M97">
-        <v>110.7639669814745</v>
+        <v>111.9299034760163</v>
       </c>
       <c r="N97">
-        <v>-101.6279669814745</v>
+        <v>-102.7939034760163</v>
       </c>
       <c r="O97">
-        <v>-22.35815273592439</v>
+        <v>-22.61465876472359</v>
       </c>
       <c r="P97">
-        <v>-79.26981424555009</v>
+        <v>-80.17924471129272</v>
       </c>
       <c r="Q97">
-        <v>-75.98981424555009</v>
+        <v>-76.89924471129272</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.133689796977703</v>
+        <v>1.405662246222129</v>
       </c>
       <c r="T97">
-        <v>25.12447568077835</v>
+        <v>31.40559460097296</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0181459734133228</v>
+        <v>0.01795695285693402</v>
       </c>
       <c r="W97">
-        <v>0.2315211794691385</v>
+        <v>0.231565750516335</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.08248169733328536</v>
+        <v>0.08162251298606371</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -10171,22 +10171,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2785296103445666</v>
+        <v>0.2804296103445666</v>
       </c>
       <c r="C98">
-        <v>-357.3602135736146</v>
+        <v>-363.2528491002777</v>
       </c>
       <c r="D98">
-        <v>117.0723109217895</v>
+        <v>116.1242746086203</v>
       </c>
       <c r="E98">
-        <v>467.4216031460248</v>
+        <v>472.3662023595186</v>
       </c>
       <c r="F98">
-        <v>474.6815244954041</v>
+        <v>479.6261237088979</v>
       </c>
       <c r="G98">
         <v>0.249</v>
@@ -10207,37 +10207,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M98">
-        <v>111.9299034760163</v>
+        <v>113.0958399705581</v>
       </c>
       <c r="N98">
-        <v>-102.7939034760163</v>
+        <v>-103.9598399705581</v>
       </c>
       <c r="O98">
-        <v>-22.61465876472359</v>
+        <v>-22.87116479352279</v>
       </c>
       <c r="P98">
-        <v>-80.17924471129271</v>
+        <v>-81.08867517703534</v>
       </c>
       <c r="Q98">
-        <v>-76.89924471129271</v>
+        <v>-77.80867517703534</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.405662246222125</v>
+        <v>1.858949661629501</v>
       </c>
       <c r="T98">
-        <v>31.40559460097287</v>
+        <v>41.8741261346305</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01795695285693402</v>
+        <v>0.01777182963160481</v>
       </c>
       <c r="W98">
-        <v>0.231565750516335</v>
+        <v>0.2316094025728676</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.08162251298606371</v>
+        <v>0.08078104378002182</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -10253,22 +10253,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2804296103445666</v>
+        <v>0.2823296103445666</v>
       </c>
       <c r="C99">
-        <v>-363.2528491002777</v>
+        <v>-369.1302538150994</v>
       </c>
       <c r="D99">
-        <v>116.1242746086203</v>
+        <v>115.1914691072923</v>
       </c>
       <c r="E99">
-        <v>472.3662023595186</v>
+        <v>477.3108015730124</v>
       </c>
       <c r="F99">
-        <v>479.6261237088979</v>
+        <v>484.5707229223917</v>
       </c>
       <c r="G99">
         <v>0.249</v>
@@ -10289,37 +10289,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M99">
-        <v>113.0958399705581</v>
+        <v>114.2617764651</v>
       </c>
       <c r="N99">
-        <v>-103.9598399705581</v>
+        <v>-105.1257764651</v>
       </c>
       <c r="O99">
-        <v>-22.87116479352279</v>
+        <v>-23.127670822322</v>
       </c>
       <c r="P99">
-        <v>-81.08867517703534</v>
+        <v>-81.99810564277797</v>
       </c>
       <c r="Q99">
-        <v>-77.80867517703534</v>
+        <v>-78.71810564277797</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.858949661629501</v>
+        <v>2.76552449244425</v>
       </c>
       <c r="T99">
-        <v>41.8741261346305</v>
+        <v>62.81118920194574</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01777182963160481</v>
+        <v>0.01759048443128231</v>
       </c>
       <c r="W99">
-        <v>0.2316094025728676</v>
+        <v>0.2316521637711036</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.08078104378002182</v>
+        <v>0.07995674741491954</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -10335,22 +10335,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2823296103445666</v>
+        <v>0.2842296103445666</v>
       </c>
       <c r="C100">
-        <v>-369.1302538150994</v>
+        <v>-374.9927918323667</v>
       </c>
       <c r="D100">
-        <v>115.1914691072923</v>
+        <v>114.2735303035188</v>
       </c>
       <c r="E100">
-        <v>477.3108015730124</v>
+        <v>482.2554007865062</v>
       </c>
       <c r="F100">
-        <v>484.5707229223917</v>
+        <v>489.5153221358855</v>
       </c>
       <c r="G100">
         <v>0.249</v>
@@ -10371,37 +10371,37 @@
         <v>9.136000000000001</v>
       </c>
       <c r="M100">
-        <v>114.2617764651</v>
+        <v>115.4277129596418</v>
       </c>
       <c r="N100">
-        <v>-105.1257764651</v>
+        <v>-106.2917129596418</v>
       </c>
       <c r="O100">
-        <v>-23.127670822322</v>
+        <v>-23.3841768511212</v>
       </c>
       <c r="P100">
-        <v>-81.99810564277797</v>
+        <v>-82.90753610852062</v>
       </c>
       <c r="Q100">
-        <v>-78.71810564277797</v>
+        <v>-79.62753610852062</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.76552449244425</v>
+        <v>5.485248984888501</v>
       </c>
       <c r="T100">
-        <v>62.81118920194574</v>
+        <v>125.6223784038915</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01759048443128231</v>
+        <v>0.01741280277036026</v>
       </c>
       <c r="W100">
-        <v>0.2316521637711036</v>
+        <v>0.2316940611067491</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -10409,91 +10409,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.07995674741491954</v>
+        <v>0.07914910350163751</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2842296103445666</v>
-      </c>
-      <c r="C101">
-        <v>-374.9927918323667</v>
-      </c>
-      <c r="D101">
-        <v>114.2735303035188</v>
-      </c>
-      <c r="E101">
-        <v>482.2554007865062</v>
-      </c>
-      <c r="F101">
-        <v>489.5153221358855</v>
-      </c>
-      <c r="G101">
-        <v>0.249</v>
-      </c>
-      <c r="H101">
-        <v>487.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>12.416</v>
-      </c>
-      <c r="K101">
-        <v>3.28</v>
-      </c>
-      <c r="L101">
-        <v>9.136000000000001</v>
-      </c>
-      <c r="M101">
-        <v>115.4277129596418</v>
-      </c>
-      <c r="N101">
-        <v>-106.2917129596418</v>
-      </c>
-      <c r="O101">
-        <v>-23.3841768511212</v>
-      </c>
-      <c r="P101">
-        <v>-82.90753610852062</v>
-      </c>
-      <c r="Q101">
-        <v>-79.62753610852062</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.485248984888501</v>
-      </c>
-      <c r="T101">
-        <v>125.6223784038915</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01741280277036026</v>
-      </c>
-      <c r="W101">
-        <v>0.2316940611067491</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.07914910350163751</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
